--- a/ИО-ЛАБ3-ПлахинДА-АП327.xlsx
+++ b/ИО-ЛАБ3-ПлахинДА-АП327.xlsx
@@ -1,19 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Games\Все что есть\Проекты\Арты\вуз\ПРЕДМЕТЫ СУа\3 курс\6 семестр\ио\РГЗ\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2122898D-71FB-4298-87A6-0CBD4EEB8921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6240" yWindow="2910" windowWidth="21600" windowHeight="11325" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6240" yWindow="2910" windowWidth="21600" windowHeight="11325" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="1" sheetId="2" r:id="rId1"/>
     <sheet name="2" sheetId="3" r:id="rId2"/>
     <sheet name="3" sheetId="4" r:id="rId3"/>
     <sheet name="4" sheetId="5" r:id="rId4"/>
@@ -22,7 +16,7 @@
     <sheet name="SPU" sheetId="8" r:id="rId7"/>
     <sheet name="8" sheetId="9" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,14 +38,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -66,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="211">
   <si>
     <t>Z=</t>
   </si>
@@ -174,27 +168,6 @@
   </si>
   <si>
     <t>1 задание</t>
-  </si>
-  <si>
-    <t>u4</t>
-  </si>
-  <si>
-    <t>u3</t>
-  </si>
-  <si>
-    <t>u2</t>
-  </si>
-  <si>
-    <t>u1</t>
-  </si>
-  <si>
-    <t>v3</t>
-  </si>
-  <si>
-    <t>v2</t>
-  </si>
-  <si>
-    <t>v1</t>
   </si>
   <si>
     <t>X</t>
@@ -931,7 +904,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
@@ -1657,7 +1630,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1887,13 +1860,17 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
-    <cellStyle name="20% — акцент5" xfId="1" builtinId="46"/>
-    <cellStyle name="20% — акцент6" xfId="2" builtinId="50"/>
-    <cellStyle name="40% — акцент6" xfId="3" builtinId="51"/>
+    <cellStyle name="20% - Акцент5" xfId="1" builtinId="46"/>
+    <cellStyle name="20% - Акцент6" xfId="2" builtinId="50"/>
+    <cellStyle name="40% - Акцент6" xfId="3" builtinId="51"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="4" xr:uid="{4AF1BDE4-E364-4877-BA7F-6CAC362AE3FA}"/>
+    <cellStyle name="Обычный 2" xfId="4"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1909,7 +1886,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
@@ -1956,26 +1933,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -2065,7 +2022,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-AE03-4C02-94FC-79EADA2EF0C5}"/>
             </c:ext>
@@ -2079,11 +2036,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1887712144"/>
-        <c:axId val="1887715472"/>
+        <c:axId val="158326080"/>
+        <c:axId val="246497280"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1887712144"/>
+        <c:axId val="158326080"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="3500"/>
@@ -2141,12 +2098,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1887715472"/>
+        <c:crossAx val="246497280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1887715472"/>
+        <c:axId val="246497280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="-1"/>
@@ -2204,7 +2161,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1887712144"/>
+        <c:crossAx val="158326080"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2254,7 +2211,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
@@ -2301,26 +2258,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -2398,7 +2335,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-5884-4F16-9C46-164F37B48C86}"/>
             </c:ext>
@@ -2412,11 +2349,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1869901600"/>
-        <c:axId val="1869903264"/>
+        <c:axId val="246499008"/>
+        <c:axId val="246499584"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1869901600"/>
+        <c:axId val="246499008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2473,12 +2410,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1869903264"/>
+        <c:crossAx val="246499584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1869903264"/>
+        <c:axId val="246499584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2535,7 +2472,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1869901600"/>
+        <c:crossAx val="246499008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2585,7 +2522,7 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
@@ -2632,26 +2569,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -2753,7 +2670,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-9E11-4CFC-BF4D-BA751C87E684}"/>
             </c:ext>
@@ -2817,7 +2734,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-9E11-4CFC-BF4D-BA751C87E684}"/>
             </c:ext>
@@ -2831,11 +2748,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1972492512"/>
-        <c:axId val="1972497920"/>
+        <c:axId val="246501312"/>
+        <c:axId val="246501888"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1972492512"/>
+        <c:axId val="246501312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="9000"/>
@@ -2893,12 +2810,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1972497920"/>
+        <c:crossAx val="246501888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1972497920"/>
+        <c:axId val="246501888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="-1"/>
@@ -2956,7 +2873,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1972492512"/>
+        <c:crossAx val="246501312"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3006,7 +2923,7 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
@@ -3053,26 +2970,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -3185,7 +3082,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-95C7-4801-9B16-161EAE18CB86}"/>
             </c:ext>
@@ -3296,7 +3193,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-95C7-4801-9B16-161EAE18CB86}"/>
             </c:ext>
@@ -3407,7 +3304,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-95C7-4801-9B16-161EAE18CB86}"/>
             </c:ext>
@@ -3518,7 +3415,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-95C7-4801-9B16-161EAE18CB86}"/>
             </c:ext>
@@ -3629,7 +3526,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000004-95C7-4801-9B16-161EAE18CB86}"/>
             </c:ext>
@@ -3740,7 +3637,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-95C7-4801-9B16-161EAE18CB86}"/>
             </c:ext>
@@ -3858,7 +3755,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-95C7-4801-9B16-161EAE18CB86}"/>
             </c:ext>
@@ -3976,7 +3873,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000007-95C7-4801-9B16-161EAE18CB86}"/>
             </c:ext>
@@ -4094,7 +3991,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000008-95C7-4801-9B16-161EAE18CB86}"/>
             </c:ext>
@@ -4212,7 +4109,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000009-95C7-4801-9B16-161EAE18CB86}"/>
             </c:ext>
@@ -4226,11 +4123,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="301383103"/>
-        <c:axId val="301383519"/>
+        <c:axId val="246503616"/>
+        <c:axId val="246504192"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="301383103"/>
+        <c:axId val="246503616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4292,26 +4189,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ru-RU"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -4350,13 +4227,13 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="301383519"/>
+        <c:crossAx val="246504192"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="301383519"/>
+        <c:axId val="246504192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4407,7 +4284,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="301383103"/>
+        <c:crossAx val="246503616"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -4488,7 +4365,7 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
@@ -4539,26 +4416,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -4671,7 +4528,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-8CEB-460E-BB73-E519DE742575}"/>
             </c:ext>
@@ -4782,7 +4639,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-8CEB-460E-BB73-E519DE742575}"/>
             </c:ext>
@@ -4893,7 +4750,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-8CEB-460E-BB73-E519DE742575}"/>
             </c:ext>
@@ -5004,7 +4861,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-8CEB-460E-BB73-E519DE742575}"/>
             </c:ext>
@@ -5115,7 +4972,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000004-8CEB-460E-BB73-E519DE742575}"/>
             </c:ext>
@@ -5226,7 +5083,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-8CEB-460E-BB73-E519DE742575}"/>
             </c:ext>
@@ -5344,7 +5201,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000006-8CEB-460E-BB73-E519DE742575}"/>
             </c:ext>
@@ -5462,7 +5319,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000007-8CEB-460E-BB73-E519DE742575}"/>
             </c:ext>
@@ -5580,7 +5437,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000008-8CEB-460E-BB73-E519DE742575}"/>
             </c:ext>
@@ -5698,7 +5555,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000009-8CEB-460E-BB73-E519DE742575}"/>
             </c:ext>
@@ -5712,11 +5569,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="301383103"/>
-        <c:axId val="301383519"/>
+        <c:axId val="246834304"/>
+        <c:axId val="246834880"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="301383103"/>
+        <c:axId val="246834304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5778,26 +5635,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ru-RU"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -5836,13 +5673,13 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="301383519"/>
+        <c:crossAx val="246834880"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="301383519"/>
+        <c:axId val="246834880"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5893,7 +5730,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="301383103"/>
+        <c:crossAx val="246834304"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5974,7 +5811,7 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
@@ -6025,26 +5862,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -6199,7 +6016,7 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
+          <c:extLst xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-7416-446B-80FD-38613B93C568}"/>
             </c:ext>
@@ -6213,11 +6030,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="436815583"/>
-        <c:axId val="436814751"/>
+        <c:axId val="246837184"/>
+        <c:axId val="246837760"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="436815583"/>
+        <c:axId val="246837184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6271,26 +6088,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ru-RU"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -6329,13 +6126,13 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="436814751"/>
+        <c:crossAx val="246837760"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="4"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="436814751"/>
+        <c:axId val="246837760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6389,26 +6186,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="ru-RU"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -6447,7 +6224,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="436815583"/>
+        <c:crossAx val="246837184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -9850,7 +9627,7 @@
         <xdr:cNvPr id="2" name="Рисунок 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0940FE38-4F63-416B-8ADF-EEC50227DB96}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0940FE38-4F63-416B-8ADF-EEC50227DB96}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9899,7 +9676,7 @@
         <xdr:cNvPr id="2" name="Диаграмма 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B92D491A-3E6D-41D0-98AD-716E87082312}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B92D491A-3E6D-41D0-98AD-716E87082312}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9937,7 +9714,7 @@
         <xdr:cNvPr id="3" name="Диаграмма 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFC6DDC4-F646-4284-A486-057B9A6EF180}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFC6DDC4-F646-4284-A486-057B9A6EF180}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9975,7 +9752,7 @@
         <xdr:cNvPr id="4" name="Диаграмма 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{422F4B2E-B5D8-49B4-90A8-982E121D4C9D}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{422F4B2E-B5D8-49B4-90A8-982E121D4C9D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10018,7 +9795,7 @@
         <xdr:cNvPr id="2" name="Диаграмма 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7A52B25-2A2F-448C-A7F0-7A47BA552CAD}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7A52B25-2A2F-448C-A7F0-7A47BA552CAD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10056,7 +9833,7 @@
         <xdr:cNvPr id="3" name="Диаграмма 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{488E1D8A-87AB-4513-9D40-62234A068014}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{488E1D8A-87AB-4513-9D40-62234A068014}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10094,7 +9871,7 @@
         <xdr:cNvPr id="4" name="Диаграмма 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E58B528B-86F3-43C0-A295-2A077046C979}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E58B528B-86F3-43C0-A295-2A077046C979}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10372,14 +10149,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7E3AE4F-ABA3-47C2-B578-361CEB6B9628}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:X75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -11186,19 +10963,19 @@
         <v>23</v>
       </c>
       <c r="D38" s="16">
-        <f>D31-(D$30*$H31)/$H$30</f>
+        <f t="shared" ref="D38:G40" si="0">D31-(D$30*$H31)/$H$30</f>
         <v>-1.01</v>
       </c>
       <c r="E38">
-        <f>E31-(E$30*$H31)/$H$30</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="F38" s="20">
-        <f>F31-(F$30*$H31)/$H$30</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G38">
-        <f>G31-(G$30*$H31)/$H$30</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H38">
@@ -11215,23 +10992,23 @@
         <v>23</v>
       </c>
       <c r="N38" s="28">
-        <f>N31-(N$30*$S31)/$S$30</f>
+        <f t="shared" ref="N38:R40" si="1">N31-(N$30*$S31)/$S$30</f>
         <v>-1.01</v>
       </c>
       <c r="O38" s="20">
-        <f>O31-(O$30*$S31)/$S$30</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="P38" s="20">
-        <f>P31-(P$30*$S31)/$S$30</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q38" s="20">
-        <f>Q31-(Q$30*$S31)/$S$30</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R38" s="27">
-        <f>R31-(R$30*$S31)/$S$30</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S38" s="20">
@@ -11250,19 +11027,19 @@
         <v>23</v>
       </c>
       <c r="D39" s="35">
-        <f>D32-(D$30*$H32)/$H$30</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E39" s="29">
-        <f>E32-(E$30*$H32)/$H$30</f>
+        <f t="shared" si="0"/>
         <v>-1.01</v>
       </c>
       <c r="F39" s="34">
-        <f>F32-(F$30*$H32)/$H$30</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="G39" s="29">
-        <f>G32-(G$30*$H32)/$H$30</f>
+        <f t="shared" si="0"/>
         <v>-1.0249999999999999</v>
       </c>
       <c r="H39" s="29">
@@ -11279,23 +11056,23 @@
         <v>23</v>
       </c>
       <c r="N39" s="8">
-        <f>N32-(N$30*$S32)/$S$30</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O39">
-        <f>O32-(O$30*$S32)/$S$30</f>
+        <f t="shared" si="1"/>
         <v>-1.01</v>
       </c>
       <c r="P39">
-        <f>P32-(P$30*$S32)/$S$30</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q39">
-        <f>Q32-(Q$30*$S32)/$S$30</f>
+        <f t="shared" si="1"/>
         <v>-1.0249999999999999</v>
       </c>
       <c r="R39" s="20">
-        <f>R32-(R$30*$S32)/$S$30</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S39">
@@ -11314,19 +11091,19 @@
         <v>0</v>
       </c>
       <c r="D40" s="33">
-        <f>D33-(D$30*$H33)/$H$30</f>
+        <f t="shared" si="0"/>
         <v>0.03</v>
       </c>
       <c r="E40" s="12">
-        <f>E33-(E$30*$H33)/$H$30</f>
+        <f t="shared" si="0"/>
         <v>-0.01</v>
       </c>
       <c r="F40" s="19">
-        <f>F33-(F$30*$H33)/$H$30</f>
+        <f t="shared" si="0"/>
         <v>-0.01</v>
       </c>
       <c r="G40" s="12">
-        <f>G33-(G$30*$H33)/$H$30</f>
+        <f t="shared" si="0"/>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="H40" s="12">
@@ -11344,23 +11121,23 @@
         <v>0</v>
       </c>
       <c r="N40" s="13">
-        <f>N33-(N$30*$S33)/$S$30</f>
+        <f t="shared" si="1"/>
         <v>0.03</v>
       </c>
       <c r="O40" s="12">
-        <f>O33-(O$30*$S33)/$S$30</f>
+        <f t="shared" si="1"/>
         <v>-0.01</v>
       </c>
       <c r="P40" s="12">
-        <f>P33-(P$30*$S33)/$S$30</f>
+        <f t="shared" si="1"/>
         <v>-0.01</v>
       </c>
       <c r="Q40" s="12">
-        <f>Q33-(Q$30*$S33)/$S$30</f>
+        <f t="shared" si="1"/>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="R40" s="19">
-        <f>R33-(R$30*$S33)/$S$30</f>
+        <f t="shared" si="1"/>
         <v>-2.5000000000000001E-2</v>
       </c>
       <c r="S40" s="12">
@@ -11470,15 +11247,15 @@
         <v>0</v>
       </c>
       <c r="G44">
-        <f>G37-(G$39*$F37)/$F$39</f>
+        <f t="shared" ref="G44:I45" si="2">G37-(G$39*$F37)/$F$39</f>
         <v>1</v>
       </c>
       <c r="H44">
-        <f>H37-(H$39*$F37)/$F$39</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I44" s="16">
-        <f>I37-(I$39*$F37)/$F$39</f>
+        <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="L44" s="8" t="s">
@@ -11534,15 +11311,15 @@
         <v>0</v>
       </c>
       <c r="G45" s="20">
-        <f>G38-(G$39*$F38)/$F$39</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H45" s="20">
-        <f>H38-(H$39*$F38)/$F$39</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I45" s="30">
-        <f>I38-(I$39*$F38)/$F$39</f>
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
       <c r="L45" s="8" t="s">
@@ -11605,19 +11382,19 @@
         <v>23</v>
       </c>
       <c r="N46" s="28">
-        <f>N39-(N$38*$R39)/$R$38</f>
+        <f t="shared" ref="N46:Q47" si="3">N39-(N$38*$R39)/$R$38</f>
         <v>0</v>
       </c>
       <c r="O46" s="20">
-        <f>O39-(O$38*$R39)/$R$38</f>
+        <f t="shared" si="3"/>
         <v>-1.01</v>
       </c>
       <c r="P46" s="27">
-        <f>P39-(P$38*$R39)/$R$38</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="Q46" s="20">
-        <f>Q39-(Q$38*$R39)/$R$38</f>
+        <f t="shared" si="3"/>
         <v>-1.0249999999999999</v>
       </c>
       <c r="R46" s="20">
@@ -11670,19 +11447,19 @@
         <v>0</v>
       </c>
       <c r="N47" s="13">
-        <f>N40-(N$38*$R40)/$R$38</f>
+        <f t="shared" si="3"/>
         <v>4.7499999999999973E-3</v>
       </c>
       <c r="O47" s="12">
-        <f>O40-(O$38*$R40)/$R$38</f>
+        <f t="shared" si="3"/>
         <v>1.5000000000000001E-2</v>
       </c>
       <c r="P47" s="19">
-        <f>P40-(P$38*$R40)/$R$38</f>
+        <f t="shared" si="3"/>
         <v>-0.01</v>
       </c>
       <c r="Q47" s="12">
-        <f>Q40-(Q$38*$R40)/$R$38</f>
+        <f t="shared" si="3"/>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="R47" s="12">
@@ -11821,19 +11598,19 @@
         <v>0</v>
       </c>
       <c r="Q51" s="10">
-        <f>Q44-(Q$46*$P44)/$P$46</f>
+        <f t="shared" ref="Q51:T52" si="4">Q44-(Q$46*$P44)/$P$46</f>
         <v>1</v>
       </c>
       <c r="R51" s="10">
-        <f>R44-(R$46*$P44)/$P$46</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S51" s="10">
-        <f>S44-(S$46*$P44)/$P$46</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="T51" s="9">
-        <f>T44-(T$46*$P44)/$P$46</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
     </row>
@@ -11880,19 +11657,19 @@
         <v>0</v>
       </c>
       <c r="Q52">
-        <f>Q45-(Q$46*$P45)/$P$46</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="R52">
-        <f>R45-(R$46*$P45)/$P$46</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="S52">
-        <f>S45-(S$46*$P45)/$P$46</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="T52" s="7">
-        <f>T45-(T$46*$P45)/$P$46</f>
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
     </row>
@@ -11912,19 +11689,19 @@
         <v>1.01</v>
       </c>
       <c r="F53" s="5">
-        <f>F46-(F$45*$E46)/$E$45</f>
+        <f t="shared" ref="F53:I54" si="5">F46-(F$45*$E46)/$E$45</f>
         <v>1</v>
       </c>
       <c r="G53" s="5">
-        <f>G46-(G$45*$E46)/$E$45</f>
+        <f t="shared" si="5"/>
         <v>-1.0249999999999999</v>
       </c>
       <c r="H53" s="5">
-        <f>H46-(H$45*$E46)/$E$45</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I53" s="16">
-        <f>I46-(I$45*$E46)/$E$45</f>
+        <f t="shared" si="5"/>
         <v>40</v>
       </c>
       <c r="J53" s="16"/>
@@ -11972,19 +11749,19 @@
         <v>2.01E-2</v>
       </c>
       <c r="F54" s="12">
-        <f>F47-(F$45*$E47)/$E$45</f>
+        <f t="shared" si="5"/>
         <v>0.01</v>
       </c>
       <c r="G54" s="12">
-        <f>G47-(G$45*$E47)/$E$45</f>
+        <f t="shared" si="5"/>
         <v>4.7500000000000007E-3</v>
       </c>
       <c r="H54" s="12">
-        <f>H47-(H$45*$E47)/$E$45</f>
+        <f t="shared" si="5"/>
         <v>0.04</v>
       </c>
       <c r="I54" s="12">
-        <f>I47-(I$45*$E47)/$E$45</f>
+        <f t="shared" si="5"/>
         <v>1.8</v>
       </c>
       <c r="L54" s="3">
@@ -12099,19 +11876,19 @@
         <v>0</v>
       </c>
       <c r="P58" s="22">
-        <f>P51-(P$53*$O51)/$O$53</f>
+        <f t="shared" ref="P58:S59" si="6">P51-(P$53*$O51)/$O$53</f>
         <v>0</v>
       </c>
       <c r="Q58" s="23">
-        <f>Q51-(Q$53*$O51)/$O$53</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="R58" s="22">
-        <f>R51-(R$53*$O51)/$O$53</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S58" s="22">
-        <f>S51-(S$53*$O51)/$O$53</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="T58" s="21">
@@ -12143,19 +11920,19 @@
         <v>0.99009900990099009</v>
       </c>
       <c r="P59">
-        <f>P52-(P$53*$O52)/$O$53</f>
+        <f t="shared" si="6"/>
         <v>0.99009900990099009</v>
       </c>
       <c r="Q59" s="20">
-        <f>Q52-(Q$53*$O52)/$O$53</f>
+        <f t="shared" si="6"/>
         <v>-1.0148514851485149</v>
       </c>
       <c r="R59">
-        <f>R52-(R$53*$O52)/$O$53</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="S59">
-        <f>S52-(S$53*$O52)/$O$53</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T59">
@@ -12332,15 +12109,15 @@
         <v>3</v>
       </c>
       <c r="N66" s="8">
-        <f>N59-(N$58*$Q59)/$Q$58</f>
+        <f t="shared" ref="N66:P68" si="7">N59-(N$58*$Q59)/$Q$58</f>
         <v>4.8514851485148558E-3</v>
       </c>
       <c r="O66">
-        <f>O59-(O$58*$Q59)/$Q$58</f>
+        <f t="shared" si="7"/>
         <v>0.99009900990099009</v>
       </c>
       <c r="P66">
-        <f>P59-(P$58*$Q59)/$Q$58</f>
+        <f t="shared" si="7"/>
         <v>0.99009900990099009</v>
       </c>
       <c r="Q66">
@@ -12348,15 +12125,15 @@
         <v>1.0148514851485149</v>
       </c>
       <c r="R66">
-        <f>R59-(R$58*$Q59)/$Q$58</f>
+        <f t="shared" ref="R66:T68" si="8">R59-(R$58*$Q59)/$Q$58</f>
         <v>1</v>
       </c>
       <c r="S66">
-        <f>S59-(S$58*$Q59)/$Q$58</f>
+        <f t="shared" si="8"/>
         <v>1.0148514851485149</v>
       </c>
       <c r="T66" s="7">
-        <f>T59-(T$58*$Q59)/$Q$58</f>
+        <f t="shared" si="8"/>
         <v>59.900990099009903</v>
       </c>
     </row>
@@ -12368,15 +12145,15 @@
         <v>1</v>
       </c>
       <c r="N67" s="8">
-        <f>N60-(N$58*$Q60)/$Q$58</f>
+        <f t="shared" si="7"/>
         <v>-1.0148514851485149</v>
       </c>
       <c r="O67">
-        <f>O60-(O$58*$Q60)/$Q$58</f>
+        <f t="shared" si="7"/>
         <v>-0.99009900990099009</v>
       </c>
       <c r="P67">
-        <f>P60-(P$58*$Q60)/$Q$58</f>
+        <f t="shared" si="7"/>
         <v>-0.99009900990099009</v>
       </c>
       <c r="Q67">
@@ -12384,15 +12161,15 @@
         <v>-1.0148514851485149</v>
       </c>
       <c r="R67">
-        <f>R60-(R$58*$Q60)/$Q$58</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S67">
-        <f>S60-(S$58*$Q60)/$Q$58</f>
+        <f t="shared" si="8"/>
         <v>-1.0148514851485149</v>
       </c>
       <c r="T67" s="7">
-        <f>T60-(T$58*$Q60)/$Q$58</f>
+        <f t="shared" si="8"/>
         <v>9.9009900990097321E-2</v>
       </c>
     </row>
@@ -12404,15 +12181,15 @@
         <v>0</v>
       </c>
       <c r="N68" s="13">
-        <f>N61-(N$58*$Q61)/$Q$58</f>
+        <f t="shared" si="7"/>
         <v>4.9727722772277203E-3</v>
       </c>
       <c r="O68" s="12">
-        <f>O61-(O$58*$Q61)/$Q$58</f>
+        <f t="shared" si="7"/>
         <v>4.8514851485148532E-3</v>
       </c>
       <c r="P68" s="12">
-        <f>P61-(P$58*$Q61)/$Q$58</f>
+        <f t="shared" si="7"/>
         <v>1.4851485148514854E-2</v>
       </c>
       <c r="Q68" s="12">
@@ -12420,15 +12197,15 @@
         <v>2.2277227722772297E-4</v>
       </c>
       <c r="R68" s="12">
-        <f>R61-(R$58*$Q61)/$Q$58</f>
+        <f t="shared" si="8"/>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="S68" s="12">
-        <f>S61-(S$58*$Q61)/$Q$58</f>
+        <f t="shared" si="8"/>
         <v>4.0222772277227724E-2</v>
       </c>
       <c r="T68" s="1">
-        <f>T61-(T$58*$Q61)/$Q$58</f>
+        <f t="shared" si="8"/>
         <v>1.9985148514851483</v>
       </c>
     </row>
@@ -12498,16 +12275,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3B43B0E-3A7E-4479-8829-88FA8349F76D}">
-  <dimension ref="B1:R42"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:O36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="2:18" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="31" t="s">
         <v>33</v>
       </c>
@@ -12518,7 +12295,7 @@
         <v>31</v>
       </c>
       <c r="E2" s="52" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F2" s="52" t="s">
         <v>30</v>
@@ -12527,25 +12304,25 @@
         <v>29</v>
       </c>
       <c r="H2" s="52" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="I2" s="52" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="J2" s="31" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K2" s="52" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="L2" s="52" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M2" s="51" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="16">
         <v>110</v>
       </c>
@@ -12583,7 +12360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B4" s="16">
         <v>1</v>
       </c>
@@ -12599,14 +12376,14 @@
       <c r="J4" s="16"/>
       <c r="M4" s="50"/>
       <c r="N4">
-        <f>SUMPRODUCT(B$3:I$3,B4:I4)</f>
+        <f t="shared" ref="N4:N9" si="0">SUMPRODUCT(B$3:I$3,B4:I4)</f>
         <v>110</v>
       </c>
       <c r="O4">
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="25"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -12628,14 +12405,14 @@
       <c r="L5" s="5"/>
       <c r="M5" s="49"/>
       <c r="N5">
-        <f>SUMPRODUCT(B$3:I$3,B5:I5)</f>
+        <f t="shared" si="0"/>
         <v>180</v>
       </c>
       <c r="O5" s="5">
         <v>180</v>
       </c>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="16">
         <v>1</v>
       </c>
@@ -12647,14 +12424,14 @@
       </c>
       <c r="M6" s="50"/>
       <c r="N6">
-        <f>SUMPRODUCT(B$3:I$3,B6:I6)</f>
+        <f t="shared" si="0"/>
         <v>150</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="16"/>
       <c r="C7">
         <v>1</v>
@@ -12668,14 +12445,14 @@
       </c>
       <c r="M7" s="50"/>
       <c r="N7">
-        <f>SUMPRODUCT(B$3:I$3,B7:I7)</f>
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="16"/>
       <c r="D8">
         <v>1</v>
@@ -12689,14 +12466,14 @@
       </c>
       <c r="M8" s="50"/>
       <c r="N8">
-        <f>SUMPRODUCT(B$3:I$3,B8:I8)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B9" s="16"/>
       <c r="E9">
         <v>1</v>
@@ -12709,14 +12486,14 @@
         <v>-80</v>
       </c>
       <c r="N9">
-        <f>SUMPRODUCT(B$3:I$3,B9:I9)</f>
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B10" s="25">
         <v>8</v>
       </c>
@@ -12758,14 +12535,9 @@
         <v>5440</v>
       </c>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="R12" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C13" s="47">
         <f>J3</f>
@@ -12783,24 +12555,8 @@
         <f>M3</f>
         <v>1</v>
       </c>
-      <c r="Q13">
-        <v>150</v>
-      </c>
-      <c r="R13">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="Q14" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="Q15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C16" s="46">
         <f>B3</f>
         <v>110</v>
@@ -12809,13 +12565,10 @@
         <f>F3</f>
         <v>40</v>
       </c>
-      <c r="Q16">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C17" s="46">
         <f>C3</f>
@@ -12825,11 +12578,8 @@
         <f>G3</f>
         <v>60</v>
       </c>
-      <c r="Q17">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="18" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C18" s="46">
         <f>D3</f>
         <v>0</v>
@@ -12855,11 +12605,8 @@
       <c r="K18">
         <v>1</v>
       </c>
-      <c r="Q18">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C19" s="46">
         <f>E3</f>
         <v>0</v>
@@ -12886,7 +12633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G20" s="43">
         <v>140</v>
       </c>
@@ -12905,7 +12652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G21" s="43">
         <v>80</v>
       </c>
@@ -12924,253 +12671,80 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="J22">
         <f>SUM(J18:J21)</f>
         <v>4660</v>
       </c>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="G23">
-        <f>SUM(G18:G21)</f>
-        <v>440</v>
-      </c>
-      <c r="M23">
-        <f>SUM(J6:M9)</f>
-        <v>-440</v>
-      </c>
-    </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="G24" s="41">
-        <v>290</v>
-      </c>
-      <c r="M24">
-        <f>600+550+560+350</f>
-        <v>2060</v>
-      </c>
-    </row>
-    <row r="26" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F26" t="s">
-        <v>42</v>
-      </c>
-      <c r="G26" t="s">
-        <v>41</v>
-      </c>
-      <c r="H26" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E27" t="s">
-        <v>39</v>
-      </c>
-      <c r="F27" s="45">
-        <v>8</v>
-      </c>
-      <c r="G27" s="44">
-        <v>12</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <f>SUMPRODUCT(B3:I3,B10:I10)</f>
-        <v>2760</v>
-      </c>
-    </row>
-    <row r="28" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E28" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" s="43">
-        <v>10</v>
-      </c>
-      <c r="G28" s="42">
-        <v>14</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E29" t="s">
-        <v>37</v>
-      </c>
-      <c r="F29" s="43">
-        <v>5</v>
-      </c>
-      <c r="G29" s="42">
-        <v>6</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E30" t="s">
-        <v>36</v>
-      </c>
-      <c r="F30" s="43">
-        <v>7</v>
-      </c>
-      <c r="G30" s="42">
-        <v>7</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="F31" t="s">
-        <v>42</v>
-      </c>
-      <c r="G31" t="s">
-        <v>41</v>
-      </c>
-      <c r="H31" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="F32" s="41">
-        <v>0</v>
-      </c>
-      <c r="G32" s="41">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D33" t="s">
-        <v>39</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-      <c r="F33" s="41">
-        <v>1</v>
-      </c>
-      <c r="G33" s="41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D34" t="s">
-        <v>38</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="G34" s="41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D35" t="s">
-        <v>37</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="G35" s="41">
-        <v>1</v>
-      </c>
-      <c r="H35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D36" t="s">
-        <v>36</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="G24" s="41"/>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D25" s="159"/>
+      <c r="E25" s="159"/>
+      <c r="F25" s="159"/>
+      <c r="G25" s="159"/>
+      <c r="H25" s="159"/>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D26" s="159"/>
+      <c r="E26" s="159"/>
+      <c r="F26" s="159"/>
+      <c r="G26" s="159"/>
+      <c r="H26" s="159"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D27" s="159"/>
+      <c r="E27" s="159"/>
+      <c r="F27" s="160"/>
+      <c r="G27" s="160"/>
+      <c r="H27" s="159"/>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D28" s="159"/>
+      <c r="E28" s="159"/>
+      <c r="F28" s="160"/>
+      <c r="G28" s="160"/>
+      <c r="H28" s="159"/>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D29" s="159"/>
+      <c r="E29" s="159"/>
+      <c r="F29" s="160"/>
+      <c r="G29" s="160"/>
+      <c r="H29" s="159"/>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D30" s="159"/>
+      <c r="E30" s="159"/>
+      <c r="F30" s="160"/>
+      <c r="G30" s="160"/>
+      <c r="H30" s="159"/>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D31" s="159"/>
+      <c r="E31" s="159"/>
+      <c r="F31" s="159"/>
+      <c r="G31" s="159"/>
+      <c r="H31" s="159"/>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="F32" s="41"/>
+      <c r="G32" s="41"/>
+    </row>
+    <row r="33" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+    </row>
+    <row r="34" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="G34" s="41"/>
+    </row>
+    <row r="35" spans="6:7" x14ac:dyDescent="0.25">
+      <c r="G35" s="41"/>
+    </row>
+    <row r="36" spans="6:7" x14ac:dyDescent="0.25">
       <c r="G36" s="41"/>
-      <c r="H36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="F38" t="s">
-        <v>42</v>
-      </c>
-      <c r="G38" t="s">
-        <v>41</v>
-      </c>
-      <c r="H38" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E39" t="s">
-        <v>39</v>
-      </c>
-      <c r="F39">
-        <f>(F$32-$E33-F27)*F33</f>
-        <v>-8</v>
-      </c>
-      <c r="G39">
-        <f>(G$32-$E33-G27)*G33</f>
-        <v>-12</v>
-      </c>
-      <c r="H39">
-        <f>(H$32-$E33-H27)*H33</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E40" t="s">
-        <v>38</v>
-      </c>
-      <c r="F40">
-        <f>(F$32-$E34-F28)*F34</f>
-        <v>0</v>
-      </c>
-      <c r="G40">
-        <f>(G$32-$E34-G28)*G34</f>
-        <v>-14</v>
-      </c>
-      <c r="H40">
-        <f>(H$32-$E34-H28)*H34</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E41" t="s">
-        <v>37</v>
-      </c>
-      <c r="F41">
-        <f>(F$32-$E35-F29)*F35</f>
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <f>(G$32-$E35-G29)*G35</f>
-        <v>-6</v>
-      </c>
-      <c r="H41">
-        <f>(H$32-$E35-H29)*H35</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="E42" t="s">
-        <v>36</v>
-      </c>
-      <c r="F42">
-        <f>(F$32-$E36-F30)*F36</f>
-        <v>0</v>
-      </c>
-      <c r="G42">
-        <f>(G$32-$E36-G30)*G36</f>
-        <v>0</v>
-      </c>
-      <c r="H42">
-        <f>(H$32-$E36-H30)*H36</f>
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13178,7 +12752,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82FCC6A5-6580-480F-9BA5-32AC959C80A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:AB87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13187,27 +12761,27 @@
   <sheetData>
     <row r="1" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="I2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="2:28" x14ac:dyDescent="0.25">
@@ -13256,7 +12830,7 @@
         <v>1800</v>
       </c>
       <c r="S4" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="2:28" x14ac:dyDescent="0.25">
@@ -13286,22 +12860,22 @@
         <v>-600</v>
       </c>
       <c r="S5" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="T5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="U5" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="V5">
         <v>1</v>
       </c>
       <c r="Y5" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="Z5" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="2:28" x14ac:dyDescent="0.25">
@@ -13583,10 +13157,10 @@
     </row>
     <row r="13" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="AA13">
         <v>0.87103587723715958</v>
@@ -13604,10 +13178,10 @@
     </row>
     <row r="16" spans="2:28" x14ac:dyDescent="0.25">
       <c r="S16" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="T16" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="4:20" x14ac:dyDescent="0.25">
@@ -13620,10 +13194,10 @@
     </row>
     <row r="18" spans="4:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E18" s="15" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -13631,7 +13205,7 @@
     </row>
     <row r="19" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D19" s="15" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E19" s="24">
         <v>3</v>
@@ -13645,7 +13219,7 @@
     </row>
     <row r="20" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D20" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E20" s="28">
         <v>-3</v>
@@ -13659,7 +13233,7 @@
     </row>
     <row r="21" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D21" s="15" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E21" s="28">
         <v>2</v>
@@ -13673,7 +13247,7 @@
     </row>
     <row r="22" spans="4:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D22" s="15" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E22" s="53">
         <v>-2</v>
@@ -13687,7 +13261,7 @@
     </row>
     <row r="23" spans="4:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D23" s="15" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E23" s="59">
         <v>27.3</v>
@@ -13701,7 +13275,7 @@
     </row>
     <row r="24" spans="4:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D24" s="15" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E24" s="58">
         <v>-235.6</v>
@@ -13715,16 +13289,16 @@
     </row>
     <row r="26" spans="4:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E26" s="15" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="Q26" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="R26">
         <v>400</v>
@@ -13732,22 +13306,22 @@
     </row>
     <row r="27" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D27" s="15" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E27" s="24">
         <f>-E19/$E$22</f>
         <v>1.5</v>
       </c>
       <c r="F27" s="10">
-        <f>F19-($E19*F$22)/$E$22</f>
+        <f t="shared" ref="F27:G29" si="0">F19-($E19*F$22)/$E$22</f>
         <v>-4</v>
       </c>
       <c r="G27" s="9">
-        <f>G19-($E19*G$22)/$E$22</f>
+        <f t="shared" si="0"/>
         <v>1200</v>
       </c>
       <c r="Q27" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -13755,41 +13329,41 @@
     </row>
     <row r="28" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D28" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E28" s="28">
         <f>-E20/$E$22</f>
         <v>-1.5</v>
       </c>
       <c r="F28">
-        <f>F20-($E20*F$22)/$E$22</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="G28" s="7">
-        <f>G20-($E20*G$22)/$E$22</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D29" s="15" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E29" s="61">
         <f>-E21/$E$22</f>
         <v>1</v>
       </c>
       <c r="F29" s="20">
-        <f>F21-($E21*F$22)/$E$22</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G29" s="26">
-        <f>G21-($E21*G$22)/$E$22</f>
+        <f t="shared" si="0"/>
         <v>400</v>
       </c>
     </row>
     <row r="30" spans="4:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D30" s="15" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E30" s="58">
         <f>1/E22</f>
@@ -13810,7 +13384,7 @@
     </row>
     <row r="31" spans="4:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D31" s="15" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E31" s="59">
         <f>-E23/$E$22</f>
@@ -13831,7 +13405,7 @@
     </row>
     <row r="32" spans="4:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D32" s="15" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E32" s="58">
         <f>-E24/$E$22</f>
@@ -13846,10 +13420,10 @@
         <v>52880</v>
       </c>
       <c r="M32" s="15" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N32" s="15" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="O32">
         <v>1</v>
@@ -13861,7 +13435,7 @@
     </row>
     <row r="33" spans="4:17" x14ac:dyDescent="0.25">
       <c r="L33" s="15" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="M33" s="11">
         <v>3</v>
@@ -13879,10 +13453,10 @@
     </row>
     <row r="34" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D34" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L34" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="M34" s="8">
         <v>-3</v>
@@ -13896,7 +13470,7 @@
     </row>
     <row r="35" spans="4:17" x14ac:dyDescent="0.25">
       <c r="L35" s="15" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M35" s="8">
         <v>2</v>
@@ -13910,7 +13484,7 @@
     </row>
     <row r="36" spans="4:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E36" s="31">
         <v>13.65</v>
@@ -13919,17 +13493,17 @@
         <v>-11220</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H36">
         <f>E31*G32-E32*G31</f>
         <v>-599904</v>
       </c>
       <c r="I36" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="L36" s="15" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="M36" s="58">
         <v>-2</v>
@@ -13949,7 +13523,7 @@
         <v>52880</v>
       </c>
       <c r="L37" s="15" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="M37" s="56">
         <v>27.3</v>
@@ -13967,7 +13541,7 @@
     </row>
     <row r="38" spans="4:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E38" s="31">
         <v>-75.5</v>
@@ -13976,17 +13550,17 @@
         <v>-11220</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H38">
         <f>E38*F39-F38*E39</f>
         <v>1260764</v>
       </c>
       <c r="I38" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="L38" s="15" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M38" s="13">
         <v>-235.6</v>
@@ -14006,24 +13580,24 @@
         <v>52880</v>
       </c>
       <c r="H39" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="4:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E40" s="15" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="G40">
         <v>1</v>
       </c>
       <c r="M40" s="15" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N40" s="15" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="O40">
         <v>1</v>
@@ -14031,7 +13605,7 @@
     </row>
     <row r="41" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D41" s="15" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E41" s="11">
         <f>-E27</f>
@@ -14046,7 +13620,7 @@
         <v>600</v>
       </c>
       <c r="L41" s="15" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="M41" s="24">
         <f>M33-($N33*M$36)/$N$36</f>
@@ -14063,7 +13637,7 @@
     </row>
     <row r="42" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D42" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E42" s="8">
         <f>-E28</f>
@@ -14078,7 +13652,7 @@
         <v>600</v>
       </c>
       <c r="L42" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="M42" s="61">
         <f>M34-($N34*M$36)/$N$36</f>
@@ -14095,7 +13669,7 @@
     </row>
     <row r="43" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D43" s="15" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E43" s="8">
         <v>1</v>
@@ -14107,7 +13681,7 @@
         <v>400</v>
       </c>
       <c r="L43" s="15" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M43" s="28">
         <f>M35-($N35*M$36)/$N$36</f>
@@ -14124,22 +13698,22 @@
     </row>
     <row r="44" spans="4:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D44" s="15" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E44" s="13">
         <f>-E30</f>
         <v>0.5</v>
       </c>
       <c r="F44" s="12">
-        <f>F30-($E30*F$29)/$E$29</f>
+        <f t="shared" ref="F44:G46" si="1">F30-($E30*F$29)/$E$29</f>
         <v>2</v>
       </c>
       <c r="G44" s="1">
-        <f>G30-($E30*G$29)/$E$29</f>
+        <f t="shared" si="1"/>
         <v>400</v>
       </c>
       <c r="L44" s="15" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M44" s="58">
         <f>M36/$N$36</f>
@@ -14156,22 +13730,22 @@
     </row>
     <row r="45" spans="4:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D45" s="15" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E45" s="56">
         <f>-E31</f>
         <v>-13.65</v>
       </c>
       <c r="F45" s="55">
-        <f>F31-($E31*F$29)/$E$29</f>
+        <f t="shared" si="1"/>
         <v>-75.5</v>
       </c>
       <c r="G45" s="54">
-        <f>G31-($E31*G$29)/$E$29</f>
+        <f t="shared" si="1"/>
         <v>-16680</v>
       </c>
       <c r="L45" s="15" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="M45" s="59">
         <f>M37-($N37*M$36)/$N$36</f>
@@ -14188,22 +13762,22 @@
     </row>
     <row r="46" spans="4:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D46" s="15" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E46" s="13">
         <f>-E32</f>
         <v>117.8</v>
       </c>
       <c r="F46" s="12">
-        <f>F32-($E32*F$29)/$E$29</f>
+        <f t="shared" si="1"/>
         <v>468.2</v>
       </c>
       <c r="G46" s="1">
-        <f>G32-($E32*G$29)/$E$29</f>
+        <f t="shared" si="1"/>
         <v>100000</v>
       </c>
       <c r="L46" s="15" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M46" s="58">
         <f>M38-($N38*M$36)/$N$36</f>
@@ -14220,7 +13794,7 @@
     </row>
     <row r="48" spans="4:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="E48" s="31">
         <v>13.65</v>
@@ -14229,17 +13803,17 @@
         <v>-16680</v>
       </c>
       <c r="G48" s="15" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H48">
         <f>E45*G46-E46*G45</f>
         <v>599904</v>
       </c>
       <c r="M48" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="N48" s="15" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="O48">
         <v>1</v>
@@ -14253,7 +13827,7 @@
         <v>100000</v>
       </c>
       <c r="L49" s="15" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="M49" s="60">
         <f>-M41/$M$42</f>
@@ -14270,7 +13844,7 @@
     </row>
     <row r="50" spans="4:15" x14ac:dyDescent="0.25">
       <c r="D50" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E50" s="31">
         <v>-75.5</v>
@@ -14279,14 +13853,14 @@
         <v>-16680</v>
       </c>
       <c r="G50" s="15" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H50">
         <f>E50*F51-F50*E51</f>
         <v>259576</v>
       </c>
       <c r="L50" s="15" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="M50" s="28">
         <f>1/M42</f>
@@ -14309,75 +13883,75 @@
         <v>100000</v>
       </c>
       <c r="L51" s="15" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M51" s="28">
         <f>-M43/$M$42</f>
         <v>0</v>
       </c>
       <c r="N51">
-        <f>N43-($M43*N$42)/$M$42</f>
+        <f t="shared" ref="N51:O54" si="2">N43-($M43*N$42)/$M$42</f>
         <v>1</v>
       </c>
       <c r="O51" s="7">
-        <f>O43-($M43*O$42)/$M$42</f>
+        <f t="shared" si="2"/>
         <v>400</v>
       </c>
     </row>
     <row r="52" spans="4:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L52" s="15" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M52" s="58">
         <f>-M44/$M$42</f>
         <v>0.25</v>
       </c>
       <c r="N52" s="12">
-        <f>N44-($M44*N$42)/$M$42</f>
+        <f t="shared" si="2"/>
         <v>-0.375</v>
       </c>
       <c r="O52" s="1">
-        <f>O44-($M44*O$42)/$M$42</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="4:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L53" s="15" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="M53" s="59">
         <f>-M45/$M$42</f>
         <v>18.875</v>
       </c>
       <c r="N53" s="55">
-        <f>N45-($M45*N$42)/$M$42</f>
+        <f t="shared" si="2"/>
         <v>-14.6625</v>
       </c>
       <c r="O53" s="54">
-        <f>O45-($M45*O$42)/$M$42</f>
+        <f t="shared" si="2"/>
         <v>-11220</v>
       </c>
     </row>
     <row r="54" spans="4:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L54" s="15" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M54" s="58">
         <f>-M46/$M$42</f>
         <v>-117.05</v>
       </c>
       <c r="N54" s="12">
-        <f>N46-($M46*N$42)/$M$42</f>
+        <f t="shared" si="2"/>
         <v>57.774999999999999</v>
       </c>
       <c r="O54" s="1">
-        <f>O46-($M46*O$42)/$M$42</f>
+        <f t="shared" si="2"/>
         <v>52880</v>
       </c>
     </row>
     <row r="56" spans="4:15" x14ac:dyDescent="0.25">
       <c r="M56" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="N56">
         <f>M53*O54-M54*O53</f>
@@ -14386,7 +13960,7 @@
     </row>
     <row r="57" spans="4:15" x14ac:dyDescent="0.25">
       <c r="M57" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="N57">
         <f>N53*O54-O53*N54</f>
@@ -14395,10 +13969,10 @@
     </row>
     <row r="59" spans="4:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M59" s="15" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="N59" s="15" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="O59">
         <v>1</v>
@@ -14406,7 +13980,7 @@
     </row>
     <row r="60" spans="4:15" x14ac:dyDescent="0.25">
       <c r="L60" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="M60" s="11">
         <v>1</v>
@@ -14420,92 +13994,92 @@
     </row>
     <row r="61" spans="4:15" x14ac:dyDescent="0.25">
       <c r="L61" s="15" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="M61" s="8">
         <f>-M50</f>
         <v>0.5</v>
       </c>
       <c r="N61" s="20">
-        <f>N50-($M50*N$49)/$M$49</f>
+        <f t="shared" ref="N61:O65" si="3">N50-($M50*N$49)/$M$49</f>
         <v>0.25</v>
       </c>
       <c r="O61" s="7">
-        <f>O50-($M50*O$49)/$M$49</f>
+        <f t="shared" si="3"/>
         <v>800</v>
       </c>
     </row>
     <row r="62" spans="4:15" x14ac:dyDescent="0.25">
       <c r="L62" s="15" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M62" s="28">
         <f>-M51</f>
         <v>0</v>
       </c>
       <c r="N62" s="27">
-        <f>N51-($M51*N$49)/$M$49</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O62" s="26">
-        <f>O51-($M51*O$49)/$M$49</f>
+        <f t="shared" si="3"/>
         <v>400</v>
       </c>
     </row>
     <row r="63" spans="4:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L63" s="15" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M63" s="13">
         <f>-M52</f>
         <v>-0.25</v>
       </c>
       <c r="N63" s="19">
-        <f>N52-($M52*N$49)/$M$49</f>
+        <f t="shared" si="3"/>
         <v>-0.375</v>
       </c>
       <c r="O63" s="1">
-        <f>O52-($M52*O$49)/$M$49</f>
+        <f t="shared" si="3"/>
         <v>-300</v>
       </c>
     </row>
     <row r="64" spans="4:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L64" s="15" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="M64" s="56">
         <f>-M53</f>
         <v>-18.875</v>
       </c>
       <c r="N64" s="57">
-        <f>N53-($M53*N$49)/$M$49</f>
+        <f t="shared" si="3"/>
         <v>-14.6625</v>
       </c>
       <c r="O64" s="54">
-        <f>O53-($M53*O$49)/$M$49</f>
+        <f t="shared" si="3"/>
         <v>-33870</v>
       </c>
     </row>
     <row r="65" spans="12:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L65" s="15" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M65" s="13">
         <f>-M54</f>
         <v>117.05</v>
       </c>
       <c r="N65" s="19">
-        <f>N54-($M54*N$49)/$M$49</f>
+        <f t="shared" si="3"/>
         <v>57.774999999999999</v>
       </c>
       <c r="O65" s="1">
-        <f>O54-($M54*O$49)/$M$49</f>
+        <f t="shared" si="3"/>
         <v>193340</v>
       </c>
     </row>
     <row r="67" spans="12:15" x14ac:dyDescent="0.25">
       <c r="M67" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="N67">
         <f>M64*O65-M65*O64</f>
@@ -14514,7 +14088,7 @@
     </row>
     <row r="68" spans="12:15" x14ac:dyDescent="0.25">
       <c r="M68" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="N68">
         <f>N64*O65-O64*N65</f>
@@ -14523,10 +14097,10 @@
     </row>
     <row r="70" spans="12:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M70" s="15" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="N70" s="15" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="O70">
         <v>1</v>
@@ -14534,7 +14108,7 @@
     </row>
     <row r="71" spans="12:15" x14ac:dyDescent="0.25">
       <c r="L71" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="M71" s="11">
         <f>M60-($N60*M$62)/$N$62</f>
@@ -14551,7 +14125,7 @@
     </row>
     <row r="72" spans="12:15" x14ac:dyDescent="0.25">
       <c r="L72" s="15" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="M72" s="8">
         <f>M61-($N61*M$62)/$N$62</f>
@@ -14568,7 +14142,7 @@
     </row>
     <row r="73" spans="12:15" x14ac:dyDescent="0.25">
       <c r="L73" s="15" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M73" s="8">
         <v>0</v>
@@ -14582,7 +14156,7 @@
     </row>
     <row r="74" spans="12:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L74" s="15" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M74" s="13">
         <f>M63-($N63*M$62)/$N$62</f>
@@ -14599,7 +14173,7 @@
     </row>
     <row r="75" spans="12:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L75" s="15" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="M75" s="56">
         <f>M64-($N64*M$62)/$N$62</f>
@@ -14616,7 +14190,7 @@
     </row>
     <row r="76" spans="12:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L76" s="15" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M76" s="13">
         <f>M65-($N65*M$62)/$N$62</f>
@@ -14633,7 +14207,7 @@
     </row>
     <row r="78" spans="12:15" x14ac:dyDescent="0.25">
       <c r="M78" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="N78">
         <f>M75*O76-M76*O75</f>
@@ -14642,7 +14216,7 @@
     </row>
     <row r="79" spans="12:15" x14ac:dyDescent="0.25">
       <c r="M79" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="N79">
         <f>N75*O76-O75*N76</f>
@@ -14651,10 +14225,10 @@
     </row>
     <row r="81" spans="12:15" x14ac:dyDescent="0.25">
       <c r="M81" s="15" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="N81" s="15" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="O81">
         <v>1</v>
@@ -14662,58 +14236,58 @@
     </row>
     <row r="82" spans="12:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L82" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="M82" s="12">
         <f>-M71/$M$74</f>
         <v>4</v>
       </c>
       <c r="N82" s="1">
-        <f>N71-($M71*N$74)/$M$74</f>
+        <f t="shared" ref="N82:O84" si="4">N71-($M71*N$74)/$M$74</f>
         <v>1.5</v>
       </c>
       <c r="O82" s="1">
-        <f>O71-($M71*O$74)/$M$74</f>
+        <f t="shared" si="4"/>
         <v>600</v>
       </c>
     </row>
     <row r="83" spans="12:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L83" s="15" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="M83" s="12">
         <f>-M72/$M$74</f>
         <v>2</v>
       </c>
       <c r="N83" s="1">
-        <f>N72-($M72*N$74)/$M$74</f>
+        <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
       <c r="O83" s="1">
-        <f>O72-($M72*O$74)/$M$74</f>
+        <f t="shared" si="4"/>
         <v>400</v>
       </c>
     </row>
     <row r="84" spans="12:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L84" s="15" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="M84" s="12">
         <f>-M73/$M$74</f>
         <v>0</v>
       </c>
       <c r="N84" s="1">
-        <f>N73-($M73*N$74)/$M$74</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="O84" s="1">
-        <f>O73-($M73*O$74)/$M$74</f>
+        <f t="shared" si="4"/>
         <v>400</v>
       </c>
     </row>
     <row r="85" spans="12:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L85" s="15" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="M85" s="53">
         <f>1/M74</f>
@@ -14730,7 +14304,7 @@
     </row>
     <row r="86" spans="12:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L86" s="15" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="M86" s="12">
         <f>-M75/$M$74</f>
@@ -14747,7 +14321,7 @@
     </row>
     <row r="87" spans="12:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L87" s="15" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M87" s="12">
         <f>-M76/$M$74</f>
@@ -14768,13 +14342,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{151B3641-A2EB-43F8-A101-B4102E5ABDD6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:AA84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="2:27" x14ac:dyDescent="0.25">
@@ -14843,7 +14417,7 @@
         <v>3</v>
       </c>
       <c r="F4">
-        <f>SUMPRODUCT(B$3:E$3,B4:E4)</f>
+        <f t="shared" ref="F4:F9" si="0">SUMPRODUCT(B$3:E$3,B4:E4)</f>
         <v>6861.17</v>
       </c>
       <c r="G4">
@@ -14876,7 +14450,7 @@
         <v>3</v>
       </c>
       <c r="F5">
-        <f>SUMPRODUCT(B$3:E$3,B5:E5)</f>
+        <f t="shared" si="0"/>
         <v>1809.5742857142855</v>
       </c>
       <c r="G5">
@@ -14903,7 +14477,7 @@
         <v>3</v>
       </c>
       <c r="F6">
-        <f>SUMPRODUCT(B$3:E$3,B6:E6)</f>
+        <f t="shared" si="0"/>
         <v>1500</v>
       </c>
       <c r="G6">
@@ -14939,7 +14513,7 @@
         <v>3</v>
       </c>
       <c r="F7">
-        <f>SUMPRODUCT(B$3:E$3,B7:E7)</f>
+        <f t="shared" si="0"/>
         <v>3500</v>
       </c>
       <c r="G7">
@@ -14975,7 +14549,7 @@
         <v>3</v>
       </c>
       <c r="F8">
-        <f>SUMPRODUCT(B$3:E$3,B8:E8)</f>
+        <f t="shared" si="0"/>
         <v>5500</v>
       </c>
       <c r="G8">
@@ -15008,7 +14582,7 @@
         <v>42</v>
       </c>
       <c r="F9">
-        <f>SUMPRODUCT(B$3:E$3,B9:E9)</f>
+        <f t="shared" si="0"/>
         <v>77222.34</v>
       </c>
       <c r="N9">
@@ -15060,7 +14634,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="K13" t="str">
         <f>"-X11"</f>
@@ -15074,7 +14648,7 @@
         <v>1</v>
       </c>
       <c r="N13" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="2:27" x14ac:dyDescent="0.25">
@@ -15082,7 +14656,7 @@
         <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D14" s="71">
         <v>3</v>
@@ -15100,7 +14674,7 @@
         <v>11</v>
       </c>
       <c r="J14" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="K14" s="71">
         <v>4</v>
@@ -15117,10 +14691,10 @@
     </row>
     <row r="15" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D15" s="16">
         <v>3</v>
@@ -15135,10 +14709,10 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="J15" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="K15" s="16">
         <v>2</v>
@@ -15155,10 +14729,10 @@
     </row>
     <row r="16" spans="2:27" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D16" s="25">
         <v>1</v>
@@ -15173,10 +14747,10 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J16" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K16" s="25">
         <v>4</v>
@@ -15196,7 +14770,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D17">
         <v>-11</v>
@@ -15214,7 +14788,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="K17">
         <v>-46</v>
@@ -15228,6 +14802,14 @@
       <c r="N17">
         <v>0</v>
       </c>
+    </row>
+    <row r="18" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="R18" s="159"/>
+      <c r="S18" s="159"/>
+      <c r="T18" s="159"/>
+      <c r="U18" s="159"/>
+      <c r="V18" s="159"/>
+      <c r="W18" s="159"/>
     </row>
     <row r="19" spans="2:23" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
@@ -15243,11 +14825,17 @@
         <v>16</v>
       </c>
       <c r="L19" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="N19" t="s">
         <v>7</v>
       </c>
+      <c r="R19" s="159"/>
+      <c r="S19" s="159"/>
+      <c r="T19" s="159"/>
+      <c r="U19" s="159"/>
+      <c r="V19" s="159"/>
+      <c r="W19" s="159"/>
     </row>
     <row r="20" spans="2:23" x14ac:dyDescent="0.25">
       <c r="D20" t="str">
@@ -15255,27 +14843,32 @@
         <v>-X11</v>
       </c>
       <c r="E20" s="50" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="K20" t="s">
         <v>10</v>
       </c>
       <c r="L20" s="50" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="M20">
         <v>1</v>
       </c>
       <c r="N20" t="s">
-        <v>81</v>
-      </c>
-      <c r="T20" s="50"/>
+        <v>74</v>
+      </c>
+      <c r="R20" s="159"/>
+      <c r="S20" s="159"/>
+      <c r="T20" s="159"/>
+      <c r="U20" s="159"/>
+      <c r="V20" s="159"/>
+      <c r="W20" s="159"/>
     </row>
     <row r="21" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
@@ -15322,16 +14915,19 @@
         <f>N14/$L$14</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="S21" s="31"/>
-      <c r="T21" s="51"/>
-      <c r="U21" s="52"/>
+      <c r="R21" s="159"/>
+      <c r="S21" s="159"/>
+      <c r="T21" s="159"/>
+      <c r="U21" s="159"/>
+      <c r="V21" s="159"/>
+      <c r="W21" s="159"/>
     </row>
     <row r="22" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D22" s="30">
         <f>D15-$E15*D$14/$E$14</f>
@@ -15342,18 +14938,18 @@
         <v>-1.5</v>
       </c>
       <c r="F22">
-        <f>F15-$E15*F$14/$E$14</f>
+        <f t="shared" ref="F22:G24" si="1">F15-$E15*F$14/$E$14</f>
         <v>3500</v>
       </c>
       <c r="G22" s="50">
-        <f>G15-$E15*G$14/$E$14</f>
+        <f t="shared" si="1"/>
         <v>-1.5</v>
       </c>
       <c r="I22" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="J22" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="K22" s="30">
         <f>-K15/$K$14</f>
@@ -15364,25 +14960,26 @@
         <v>-1</v>
       </c>
       <c r="M22" s="20">
-        <f>M15-$L15*M$14/$L$14</f>
+        <f t="shared" ref="M22:N24" si="2">M15-$L15*M$14/$L$14</f>
         <v>3500</v>
       </c>
       <c r="N22" s="65">
-        <f>N15-$L15*N$14/$L$14</f>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
-      <c r="S22" s="16"/>
-      <c r="T22" s="50"/>
-      <c r="U22" s="51"/>
-      <c r="V22" s="51"/>
-      <c r="W22" s="51"/>
+      <c r="R22" s="159"/>
+      <c r="S22" s="159"/>
+      <c r="T22" s="159"/>
+      <c r="U22" s="159"/>
+      <c r="V22" s="159"/>
+      <c r="W22" s="159"/>
     </row>
     <row r="23" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D23" s="70">
         <f>D16-$E16*D$14/$E$14</f>
@@ -15393,18 +14990,18 @@
         <v>-1.5</v>
       </c>
       <c r="F23" s="29">
-        <f>F16-$E16*F$14/$E$14</f>
+        <f t="shared" si="1"/>
         <v>1500</v>
       </c>
       <c r="G23" s="66">
-        <f>G16-$E16*G$14/$E$14</f>
+        <f t="shared" si="1"/>
         <v>-1.5</v>
       </c>
       <c r="I23" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J23" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K23" s="25">
         <f>K16-$L16*K$14/$L$14</f>
@@ -15415,22 +15012,26 @@
         <v>-1</v>
       </c>
       <c r="M23" s="5">
-        <f>M16-$L16*M$14/$L$14</f>
+        <f t="shared" si="2"/>
         <v>5500</v>
       </c>
       <c r="N23" s="49">
-        <f>N16-$L16*N$14/$L$14</f>
+        <f t="shared" si="2"/>
         <v>-1</v>
       </c>
-      <c r="S23" s="25"/>
-      <c r="T23" s="51"/>
+      <c r="R23" s="159"/>
+      <c r="S23" s="159"/>
+      <c r="T23" s="159"/>
+      <c r="U23" s="159"/>
+      <c r="V23" s="159"/>
+      <c r="W23" s="159"/>
     </row>
     <row r="24" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D24" s="20">
         <f>D17-$E17*D$14/$E$14</f>
@@ -15441,18 +15042,18 @@
         <v>9.5</v>
       </c>
       <c r="F24">
-        <f>F17-$E17*F$14/$E$14</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G24">
-        <f>G17-$E17*G$14/$E$14</f>
+        <f t="shared" si="1"/>
         <v>9.5</v>
       </c>
       <c r="I24">
         <v>1</v>
       </c>
       <c r="J24" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="K24">
         <f>K17-$L17*K$14/$L$14</f>
@@ -15463,18 +15064,23 @@
         <v>14</v>
       </c>
       <c r="M24">
-        <f>M17-$L17*M$14/$L$14</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N24">
-        <f>N17-$L17*N$14/$L$14</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="T24" s="51"/>
+      <c r="R24" s="159"/>
+      <c r="S24" s="159"/>
+      <c r="T24" s="159"/>
+      <c r="U24" s="159"/>
+      <c r="V24" s="159"/>
+      <c r="W24" s="159"/>
     </row>
     <row r="26" spans="2:23" x14ac:dyDescent="0.25">
       <c r="D26" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E26" s="50" t="s">
         <v>11</v>
@@ -15486,7 +15092,7 @@
         <v>16</v>
       </c>
       <c r="L26" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="N26" t="s">
         <v>7</v>
@@ -15494,28 +15100,28 @@
     </row>
     <row r="27" spans="2:23" x14ac:dyDescent="0.25">
       <c r="D27" s="31" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F27" s="52">
         <v>1</v>
       </c>
       <c r="G27" s="51" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="K27" t="s">
         <v>10</v>
       </c>
       <c r="L27" s="50" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="M27">
         <v>1</v>
       </c>
       <c r="N27" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="2:23" x14ac:dyDescent="0.25">
@@ -15530,15 +15136,15 @@
         <v>0.42857142857142855</v>
       </c>
       <c r="E28" s="65">
-        <f>E21-$D21*E$23/$D$23</f>
+        <f t="shared" ref="E28:G29" si="3">E21-$D21*E$23/$D$23</f>
         <v>-0.1428571428571429</v>
       </c>
       <c r="F28">
-        <f>F21-$D21*F$23/$D$23</f>
+        <f t="shared" si="3"/>
         <v>642.85714285714289</v>
       </c>
       <c r="G28" s="50">
-        <f>G21-$D21*G$23/$D$23</f>
+        <f t="shared" si="3"/>
         <v>-0.1428571428571429</v>
       </c>
       <c r="I28" t="s">
@@ -15565,32 +15171,32 @@
     </row>
     <row r="29" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C29" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D29" s="35">
         <f>-D22/$D$23</f>
         <v>-0.42857142857142855</v>
       </c>
       <c r="E29" s="67">
-        <f>E22-$D22*E$23/$D$23</f>
+        <f t="shared" si="3"/>
         <v>-0.8571428571428571</v>
       </c>
       <c r="F29" s="29">
-        <f>F22-$D22*F$23/$D$23</f>
+        <f t="shared" si="3"/>
         <v>2857.1428571428569</v>
       </c>
       <c r="G29" s="66">
-        <f>G22-$D22*G$23/$D$23</f>
+        <f t="shared" si="3"/>
         <v>-0.8571428571428571</v>
       </c>
       <c r="I29" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J29" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="K29" s="20">
         <f>-K22</f>
@@ -15610,10 +15216,10 @@
     </row>
     <row r="30" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D30">
         <f>1/D23</f>
@@ -15632,10 +15238,10 @@
         <v>0.42857142857142855</v>
       </c>
       <c r="I30" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J30" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="K30">
         <f>K23-$L23*K$22/$L$22</f>
@@ -15658,7 +15264,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D31">
         <f>-D24/$D$23</f>
@@ -15680,7 +15286,7 @@
         <v>1</v>
       </c>
       <c r="J31" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="K31">
         <f>K24-$L24*K$22/$L$22</f>
@@ -15700,7 +15306,7 @@
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D33" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E33" s="50" t="s">
         <v>11</v>
@@ -15711,16 +15317,16 @@
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.25">
       <c r="D34" s="31" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E34" s="51" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F34" s="52">
         <v>1</v>
       </c>
       <c r="G34" s="51" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.25">
@@ -15755,10 +15361,10 @@
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C36" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D36" s="35">
         <f>D29/$E$29</f>
@@ -15785,10 +15391,10 @@
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="D37">
         <f>D30-$E30*D$29/$E$29</f>
@@ -15818,7 +15424,7 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D38">
         <f>D31-$E31*D$29/$E$29</f>
@@ -16021,21 +15627,21 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D501F0E0-DDDC-4263-848E-5E0BD7360088}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:U122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -16090,28 +15696,28 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B9" s="15" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="K9">
         <v>1</v>
       </c>
       <c r="O9" s="15" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="P9" s="15" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="Q9">
         <v>1</v>
@@ -16119,7 +15725,7 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B10" s="74">
         <v>2</v>
@@ -16131,7 +15737,7 @@
         <v>33</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="I10" s="74">
         <v>2</v>
@@ -16143,7 +15749,7 @@
         <v>33</v>
       </c>
       <c r="N10" s="15" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O10" s="74">
         <v>2</v>
@@ -16157,7 +15763,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B11" s="74">
         <v>3</v>
@@ -16169,7 +15775,7 @@
         <v>58</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="I11" s="74">
         <v>3</v>
@@ -16181,7 +15787,7 @@
         <v>58</v>
       </c>
       <c r="N11" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="O11" s="74">
         <v>3</v>
@@ -16195,7 +15801,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B12" s="74">
         <v>-14</v>
@@ -16207,7 +15813,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -16219,7 +15825,7 @@
         <v>8</v>
       </c>
       <c r="N12" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="O12" s="27">
         <v>1</v>
@@ -16233,7 +15839,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H13" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="I13" s="74">
         <v>-14</v>
@@ -16245,7 +15851,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="O13" s="74">
         <v>-14</v>
@@ -16259,10 +15865,10 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B14" s="15" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -16270,7 +15876,7 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B15" s="74">
         <f>B10/$C$10</f>
@@ -16285,19 +15891,19 @@
         <v>16.5</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
       <c r="O15" s="15" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="P15" s="15" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="Q15">
         <v>1</v>
@@ -16305,7 +15911,7 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B16" s="75">
         <f>B11-B$10*$C11/$C$10</f>
@@ -16320,7 +15926,7 @@
         <v>-8</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="I16" s="75">
         <f>I10-I$12*$J10/$J$12</f>
@@ -16335,7 +15941,7 @@
         <v>17</v>
       </c>
       <c r="N16" s="15" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O16" s="74">
         <v>-2</v>
@@ -16349,7 +15955,7 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B17" s="74">
         <f>B12-B$10*$C12/$C$10</f>
@@ -16364,7 +15970,7 @@
         <v>297</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="I17" s="74">
         <f>I11-I$12*$J11/$J$12</f>
@@ -16379,7 +15985,7 @@
         <v>26</v>
       </c>
       <c r="N17" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="O17" s="74">
         <v>-3</v>
@@ -16393,7 +15999,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H18" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -16405,7 +16011,7 @@
         <v>8</v>
       </c>
       <c r="N18" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="O18">
         <v>1</v>
@@ -16419,16 +16025,16 @@
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D19">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="I19" s="74">
         <f>I13-I$12*$J13/$J$12</f>
@@ -16443,7 +16049,7 @@
         <v>144</v>
       </c>
       <c r="N19" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="O19" s="74">
         <v>14</v>
@@ -16457,7 +16063,7 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -16473,7 +16079,7 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B21" s="27">
         <v>-1</v>
@@ -16487,19 +16093,19 @@
         <v>8</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="K21">
         <v>1</v>
       </c>
       <c r="O21" s="15" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="P21" s="15" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="Q21">
         <v>1</v>
@@ -16507,7 +16113,7 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B22">
         <v>4</v>
@@ -16521,7 +16127,7 @@
         <v>265</v>
       </c>
       <c r="H22" s="15" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="I22" s="75">
         <f>1/I16</f>
@@ -16536,7 +16142,7 @@
         <v>8.5</v>
       </c>
       <c r="N22" s="15" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="O22" s="74">
         <v>-0.5</v>
@@ -16550,7 +16156,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H23" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="I23" s="74">
         <f>-I17/$I$16</f>
@@ -16563,7 +16169,7 @@
         <v>26</v>
       </c>
       <c r="N23" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="O23" s="74">
         <v>-0.75</v>
@@ -16577,7 +16183,7 @@
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H24" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="I24" s="74">
         <f>-I18/$I$16</f>
@@ -16592,7 +16198,7 @@
         <v>8</v>
       </c>
       <c r="N24" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="O24" s="74">
         <v>1</v>
@@ -16606,7 +16212,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H25" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="I25" s="74">
         <f>-I19/$I$16</f>
@@ -16621,7 +16227,7 @@
         <v>263</v>
       </c>
       <c r="N25" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="O25" s="74">
         <v>0.5</v>
@@ -16635,19 +16241,19 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E31" s="15" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="N31" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="O31" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="P31">
         <v>1</v>
@@ -16655,7 +16261,7 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D32" s="15" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E32" s="74">
         <v>2</v>
@@ -16667,7 +16273,7 @@
         <v>33</v>
       </c>
       <c r="M32" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="N32">
         <v>2</v>
@@ -16681,7 +16287,7 @@
     </row>
     <row r="33" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D33" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E33" s="74">
         <v>3</v>
@@ -16693,7 +16299,7 @@
         <v>58</v>
       </c>
       <c r="M33" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="N33">
         <v>3</v>
@@ -16707,7 +16313,7 @@
     </row>
     <row r="34" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D34" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -16719,7 +16325,7 @@
         <v>-9</v>
       </c>
       <c r="M34" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -16733,7 +16339,7 @@
     </row>
     <row r="35" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D35" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E35" s="74">
         <v>-14</v>
@@ -16745,7 +16351,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="N35" s="27">
         <v>-1</v>
@@ -16759,7 +16365,7 @@
     </row>
     <row r="36" spans="4:16" x14ac:dyDescent="0.25">
       <c r="M36" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="N36">
         <v>-14</v>
@@ -16773,10 +16379,10 @@
     </row>
     <row r="37" spans="4:16" x14ac:dyDescent="0.25">
       <c r="E37" s="15" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -16784,7 +16390,7 @@
     </row>
     <row r="38" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D38" s="15" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E38" s="74">
         <f>E32-E$34*$F32/$F$34</f>
@@ -16798,10 +16404,10 @@
         <v>15</v>
       </c>
       <c r="N38" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="O38" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="P38">
         <v>1</v>
@@ -16809,7 +16415,7 @@
     </row>
     <row r="39" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D39" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E39" s="75">
         <f>E33-E$34*$F33/$F$34</f>
@@ -16823,23 +16429,23 @@
         <v>22</v>
       </c>
       <c r="M39" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="N39">
         <v>2</v>
       </c>
       <c r="O39" s="74">
-        <f>O32-O$35*$N32/$N$35</f>
+        <f t="shared" ref="O39:P41" si="0">O32-O$35*$N32/$N$35</f>
         <v>2</v>
       </c>
       <c r="P39" s="74">
-        <f>P32-P$35*$N32/$N$35</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
     </row>
     <row r="40" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D40" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -16852,23 +16458,23 @@
         <v>9</v>
       </c>
       <c r="M40" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="N40">
         <v>3</v>
       </c>
       <c r="O40" s="74">
-        <f>O33-O$35*$N33/$N$35</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="P40" s="74">
-        <f>P33-P$35*$N33/$N$35</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
     </row>
     <row r="41" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D41" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E41" s="74">
         <f>E35-E$34*$F35/$F$34</f>
@@ -16882,23 +16488,23 @@
         <v>162</v>
       </c>
       <c r="M41" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="N41">
         <v>0</v>
       </c>
       <c r="O41" s="75">
-        <f>O34-O$35*$N34/$N$35</f>
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
       <c r="P41" s="74">
-        <f>P34-P$35*$N34/$N$35</f>
+        <f t="shared" si="0"/>
         <v>-9</v>
       </c>
     </row>
     <row r="42" spans="4:16" x14ac:dyDescent="0.25">
       <c r="M42" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -16912,16 +16518,16 @@
     </row>
     <row r="43" spans="4:16" x14ac:dyDescent="0.25">
       <c r="E43" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F43" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G43">
         <v>1</v>
       </c>
       <c r="M43" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="N43">
         <v>-14</v>
@@ -16937,7 +16543,7 @@
     </row>
     <row r="44" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D44" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E44">
         <f>-E38/$E$39</f>
@@ -16955,7 +16561,7 @@
     </row>
     <row r="45" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D45" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E45">
         <f>1/E39</f>
@@ -16972,7 +16578,7 @@
     </row>
     <row r="46" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D46" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E46">
         <f>-E40/$E$39</f>
@@ -16987,10 +16593,10 @@
         <v>9</v>
       </c>
       <c r="N46" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="O46" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="P46">
         <v>1</v>
@@ -16998,7 +16604,7 @@
     </row>
     <row r="47" spans="4:16" x14ac:dyDescent="0.25">
       <c r="D47" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E47">
         <f>-E41/$E$39</f>
@@ -17013,7 +16619,7 @@
         <v>264.66666666666669</v>
       </c>
       <c r="M47" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="N47" s="74">
         <f>N39-N$41*$O39/$O$41</f>
@@ -17029,7 +16635,7 @@
     </row>
     <row r="48" spans="4:16" x14ac:dyDescent="0.25">
       <c r="M48" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="N48" s="74">
         <f>N40-N$41*$O40/$O$41</f>
@@ -17045,7 +16651,7 @@
     </row>
     <row r="49" spans="2:16" x14ac:dyDescent="0.25">
       <c r="M49" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="N49">
         <v>0</v>
@@ -17059,25 +16665,25 @@
     </row>
     <row r="50" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C50" s="15" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E50">
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I50" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="J50">
         <v>1</v>
       </c>
       <c r="M50" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="N50" s="74">
         <f>N42-N$41*$O42/$O$41</f>
@@ -17092,7 +16698,7 @@
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C51" s="74">
         <v>2</v>
@@ -17104,7 +16710,7 @@
         <v>33</v>
       </c>
       <c r="G51" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H51">
         <v>2</v>
@@ -17116,7 +16722,7 @@
         <v>33</v>
       </c>
       <c r="M51" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="N51" s="74">
         <f>N43-N$41*$O43/$O$41</f>
@@ -17132,7 +16738,7 @@
     </row>
     <row r="52" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C52" s="74">
         <v>3</v>
@@ -17144,7 +16750,7 @@
         <v>58</v>
       </c>
       <c r="G52" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H52">
         <v>3</v>
@@ -17158,7 +16764,7 @@
     </row>
     <row r="53" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -17170,7 +16776,7 @@
         <v>-9</v>
       </c>
       <c r="G53" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -17184,7 +16790,7 @@
     </row>
     <row r="54" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C54" s="27">
         <v>1</v>
@@ -17196,7 +16802,7 @@
         <v>7</v>
       </c>
       <c r="G54" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H54" s="27">
         <v>1</v>
@@ -17210,7 +16816,7 @@
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C55" s="74">
         <v>-14</v>
@@ -17222,7 +16828,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H55">
         <v>-14</v>
@@ -17240,19 +16846,19 @@
     </row>
     <row r="57" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C57" s="15" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E57">
         <v>1</v>
       </c>
       <c r="H57" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="I57" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -17260,7 +16866,7 @@
     </row>
     <row r="58" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C58" s="74">
         <v>-2</v>
@@ -17274,23 +16880,23 @@
         <v>19</v>
       </c>
       <c r="G58" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H58">
         <v>-2</v>
       </c>
       <c r="I58" s="74">
-        <f>I51-I$54*$H51/$H$54</f>
+        <f t="shared" ref="I58:J60" si="1">I51-I$54*$H51/$H$54</f>
         <v>2</v>
       </c>
       <c r="J58" s="74">
-        <f>J51-J$54*$H51/$H$54</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
     </row>
     <row r="59" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C59" s="74">
         <v>-3</v>
@@ -17304,23 +16910,23 @@
         <v>37</v>
       </c>
       <c r="G59" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H59">
         <v>-3</v>
       </c>
       <c r="I59" s="75">
-        <f>I52-I$54*$H52/$H$54</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="J59" s="74">
-        <f>J52-J$54*$H52/$H$54</f>
+        <f t="shared" si="1"/>
         <v>37</v>
       </c>
     </row>
     <row r="60" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -17332,23 +16938,23 @@
         <v>-9</v>
       </c>
       <c r="G60" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H60">
         <v>0</v>
       </c>
       <c r="I60" s="74">
-        <f>I53-I$54*$H53/$H$54</f>
+        <f t="shared" si="1"/>
         <v>-1</v>
       </c>
       <c r="J60" s="74">
-        <f>J53-J$54*$H53/$H$54</f>
+        <f t="shared" si="1"/>
         <v>-10</v>
       </c>
     </row>
     <row r="61" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -17360,7 +16966,7 @@
         <v>7</v>
       </c>
       <c r="G61" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -17374,7 +16980,7 @@
     </row>
     <row r="62" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C62" s="74">
         <v>14</v>
@@ -17388,7 +16994,7 @@
         <v>98</v>
       </c>
       <c r="G62" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H62">
         <v>14</v>
@@ -17408,19 +17014,19 @@
     </row>
     <row r="64" spans="2:16" x14ac:dyDescent="0.25">
       <c r="C64" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D64" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E64">
         <v>1</v>
       </c>
       <c r="H64" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I64" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -17428,7 +17034,7 @@
     </row>
     <row r="65" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C65" s="74">
         <f>C58-C$59*$D58/$D$59</f>
@@ -17443,7 +17049,7 @@
         <v>0.5</v>
       </c>
       <c r="G65" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H65" s="74">
         <f>H58-H$59*$I58/$I$59</f>
@@ -17459,7 +17065,7 @@
     </row>
     <row r="66" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C66" s="74">
         <f>C59/$D$59</f>
@@ -17474,7 +17080,7 @@
         <v>9.25</v>
       </c>
       <c r="G66" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H66" s="74">
         <f>H59/$I$59</f>
@@ -17491,7 +17097,7 @@
     </row>
     <row r="67" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C67" s="74">
         <f>C60-C$59*$D60/$D$59</f>
@@ -17506,7 +17112,7 @@
         <v>0.25</v>
       </c>
       <c r="G67" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H67" s="74">
         <f>H60-H$59*$I60/$I$59</f>
@@ -17521,12 +17127,12 @@
         <v>-0.75</v>
       </c>
       <c r="K67" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C68" s="74">
         <f>C61-C$59*$D61/$D$59</f>
@@ -17541,7 +17147,7 @@
         <v>7</v>
       </c>
       <c r="G68" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="H68" s="74">
         <f>H61-H$59*$I61/$I$59</f>
@@ -17558,7 +17164,7 @@
     </row>
     <row r="69" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C69" s="74">
         <f>C62-C$59*$D62/$D$59</f>
@@ -17573,7 +17179,7 @@
         <v>264.5</v>
       </c>
       <c r="G69" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H69" s="74">
         <f>H62-H$59*$I62/$I$59</f>
@@ -17590,19 +17196,19 @@
     </row>
     <row r="77" spans="2:21" x14ac:dyDescent="0.25">
       <c r="L77" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="M77" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="N77">
         <v>1</v>
       </c>
       <c r="S77" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="T77" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="U77">
         <v>1</v>
@@ -17610,7 +17216,7 @@
     </row>
     <row r="78" spans="2:21" x14ac:dyDescent="0.25">
       <c r="K78" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="L78">
         <v>2</v>
@@ -17622,7 +17228,7 @@
         <v>33</v>
       </c>
       <c r="R78" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="S78">
         <v>2</v>
@@ -17636,16 +17242,16 @@
     </row>
     <row r="79" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C79" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D79" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E79">
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="L79">
         <v>3</v>
@@ -17657,7 +17263,7 @@
         <v>58</v>
       </c>
       <c r="R79" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="S79">
         <v>3</v>
@@ -17671,7 +17277,7 @@
     </row>
     <row r="80" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C80">
         <v>2</v>
@@ -17683,7 +17289,7 @@
         <v>33</v>
       </c>
       <c r="K80" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="L80">
         <v>0</v>
@@ -17695,7 +17301,7 @@
         <v>7</v>
       </c>
       <c r="R80" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -17709,7 +17315,7 @@
     </row>
     <row r="81" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C81">
         <v>3</v>
@@ -17721,7 +17327,7 @@
         <v>58</v>
       </c>
       <c r="K81" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="L81" s="27">
         <v>-1</v>
@@ -17733,7 +17339,7 @@
         <v>-9</v>
       </c>
       <c r="R81" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="S81" s="27">
         <v>-1</v>
@@ -17747,7 +17353,7 @@
     </row>
     <row r="82" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -17759,7 +17365,7 @@
         <v>8</v>
       </c>
       <c r="K82" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L82">
         <v>-14</v>
@@ -17771,7 +17377,7 @@
         <v>0</v>
       </c>
       <c r="R82" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="S82">
         <v>-14</v>
@@ -17785,7 +17391,7 @@
     </row>
     <row r="83" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C83" s="27">
         <v>1</v>
@@ -17799,7 +17405,7 @@
     </row>
     <row r="84" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C84">
         <v>-14</v>
@@ -17811,19 +17417,19 @@
         <v>0</v>
       </c>
       <c r="L84" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="M84" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="N84">
         <v>1</v>
       </c>
       <c r="S84" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="T84" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="U84">
         <v>1</v>
@@ -17831,76 +17437,76 @@
     </row>
     <row r="85" spans="2:21" x14ac:dyDescent="0.25">
       <c r="K85" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="L85">
         <v>2</v>
       </c>
       <c r="M85" s="27">
-        <f>M78-M$81*$L78/$L$81</f>
+        <f t="shared" ref="M85:N87" si="2">M78-M$81*$L78/$L$81</f>
         <v>2</v>
       </c>
       <c r="N85">
-        <f>N78-N$81*$L78/$L$81</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="R85" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="S85">
         <v>2</v>
       </c>
       <c r="T85" s="27">
-        <f>T78-T$81*$L78/$L$81</f>
+        <f t="shared" ref="T85:U87" si="3">T78-T$81*$L78/$L$81</f>
         <v>2</v>
       </c>
       <c r="U85">
-        <f>U78-U$81*$L78/$L$81</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
     </row>
     <row r="86" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C86" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D86" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E86">
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="L86">
         <v>3</v>
       </c>
       <c r="M86">
-        <f>M79-M$81*$L79/$L$81</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="N86">
-        <f>N79-N$81*$L79/$L$81</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="R86" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="S86">
         <v>3</v>
       </c>
       <c r="T86">
-        <f>T79-T$81*$L79/$L$81</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="U86">
-        <f>U79-U$81*$L79/$L$81</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
     </row>
     <row r="87" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C87">
         <v>-2</v>
@@ -17914,37 +17520,37 @@
         <v>17</v>
       </c>
       <c r="K87" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="L87">
         <v>0</v>
       </c>
       <c r="M87">
-        <f>M80-M$81*$L80/$L$81</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N87">
-        <f>N80-N$81*$L80/$L$81</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
       <c r="R87" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="S87">
         <v>0</v>
       </c>
       <c r="T87">
-        <f>T80-T$81*$L80/$L$81</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="U87">
-        <f>U80-U$81*$L80/$L$81</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
     </row>
     <row r="88" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B88" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C88">
         <v>-3</v>
@@ -17958,7 +17564,7 @@
         <v>34</v>
       </c>
       <c r="K88" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="L88">
         <v>-1</v>
@@ -17970,7 +17576,7 @@
         <v>9</v>
       </c>
       <c r="R88" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="S88">
         <v>-1</v>
@@ -17984,7 +17590,7 @@
     </row>
     <row r="89" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -17996,7 +17602,7 @@
         <v>8</v>
       </c>
       <c r="K89" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L89">
         <v>-14</v>
@@ -18010,7 +17616,7 @@
         <v>126</v>
       </c>
       <c r="R89" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="S89">
         <v>-14</v>
@@ -18026,7 +17632,7 @@
     </row>
     <row r="90" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -18041,7 +17647,7 @@
     </row>
     <row r="91" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C91">
         <v>14</v>
@@ -18055,19 +17661,19 @@
         <v>112</v>
       </c>
       <c r="L91" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="M91" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="N91">
         <v>1</v>
       </c>
       <c r="S91" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="T91" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="U91">
         <v>1</v>
@@ -18075,7 +17681,7 @@
     </row>
     <row r="92" spans="2:21" x14ac:dyDescent="0.25">
       <c r="K92" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="L92">
         <f>L85/$M$85</f>
@@ -18090,7 +17696,7 @@
         <v>7.5</v>
       </c>
       <c r="R92" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="S92">
         <f>S85/$M$85</f>
@@ -18107,16 +17713,16 @@
     </row>
     <row r="93" spans="2:21" x14ac:dyDescent="0.25">
       <c r="C93" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D93" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E93">
         <v>1</v>
       </c>
       <c r="K93" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="L93">
         <f>L86-L$85*$M86/$M$85</f>
@@ -18130,7 +17736,7 @@
         <v>1</v>
       </c>
       <c r="R93" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="S93">
         <f>S86-S$85*$M86/$M$85</f>
@@ -18146,7 +17752,7 @@
     </row>
     <row r="94" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C94">
         <f>C87-$D87*C$89/$D$89</f>
@@ -18160,7 +17766,7 @@
         <v>1</v>
       </c>
       <c r="K94" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="L94">
         <f>L87-L$85*$M87/$M$85</f>
@@ -18175,7 +17781,7 @@
         <v>-0.5</v>
       </c>
       <c r="R94" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="S94">
         <f>S87-S$85*$M87/$M$85</f>
@@ -18192,7 +17798,7 @@
     </row>
     <row r="95" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B95" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C95">
         <f>C88-$D88*C$89/$D$89</f>
@@ -18206,7 +17812,7 @@
         <v>2</v>
       </c>
       <c r="K95" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="L95">
         <f>L88-L$85*$M88/$M$85</f>
@@ -18221,7 +17827,7 @@
         <v>9</v>
       </c>
       <c r="R95" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="S95">
         <f>S88-S$85*$M88/$M$85</f>
@@ -18238,7 +17844,7 @@
     </row>
     <row r="96" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -18250,7 +17856,7 @@
         <v>8</v>
       </c>
       <c r="K96" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L96">
         <f>L89-L$85*$M89/$M$85</f>
@@ -18265,7 +17871,7 @@
         <v>261</v>
       </c>
       <c r="R96" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="S96">
         <f>S89-S$85*$M89/$M$85</f>
@@ -18282,7 +17888,7 @@
     </row>
     <row r="97" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C97">
         <f>C90-$D90*C$89/$D$89</f>
@@ -18298,7 +17904,7 @@
     </row>
     <row r="98" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C98">
         <f>C91-$D91*C$89/$D$89</f>
@@ -18314,19 +17920,19 @@
     </row>
     <row r="100" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E100" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F100" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G100">
         <v>1</v>
       </c>
       <c r="J100" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="K100" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="L100">
         <v>1</v>
@@ -18334,7 +17940,7 @@
     </row>
     <row r="101" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D101" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E101">
         <v>2</v>
@@ -18346,7 +17952,7 @@
         <v>33</v>
       </c>
       <c r="I101" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="J101">
         <v>2</v>
@@ -18360,7 +17966,7 @@
     </row>
     <row r="102" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D102" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E102">
         <v>3</v>
@@ -18372,7 +17978,7 @@
         <v>58</v>
       </c>
       <c r="I102" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J102">
         <v>3</v>
@@ -18386,7 +17992,7 @@
     </row>
     <row r="103" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D103" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -18398,7 +18004,7 @@
         <v>8</v>
       </c>
       <c r="I103" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J103" s="27">
         <v>1</v>
@@ -18412,7 +18018,7 @@
     </row>
     <row r="104" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D104" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E104">
         <v>1</v>
@@ -18424,7 +18030,7 @@
         <v>9</v>
       </c>
       <c r="I104" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -18438,7 +18044,7 @@
     </row>
     <row r="105" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D105" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E105">
         <v>-1</v>
@@ -18450,7 +18056,7 @@
         <v>-9</v>
       </c>
       <c r="I105" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -18464,7 +18070,7 @@
     </row>
     <row r="106" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D106" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E106">
         <v>-14</v>
@@ -18476,7 +18082,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="J106">
         <v>-14</v>
@@ -18490,19 +18096,19 @@
     </row>
     <row r="108" spans="2:12" x14ac:dyDescent="0.25">
       <c r="E108" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F108" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G108">
         <v>1</v>
       </c>
       <c r="J108" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="K108" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="L108">
         <v>1</v>
@@ -18510,7 +18116,7 @@
     </row>
     <row r="109" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D109" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E109">
         <f>E101-$F101*E$103/$F$103</f>
@@ -18520,11 +18126,11 @@
         <v>-2</v>
       </c>
       <c r="G109">
-        <f>G101-$F101*G$103/$F$103</f>
+        <f t="shared" ref="G109:G114" si="4">G101-$F101*G$103/$F$103</f>
         <v>17</v>
       </c>
       <c r="I109" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="J109">
         <v>-2</v>
@@ -18540,7 +18146,7 @@
     </row>
     <row r="110" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D110" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E110">
         <f>E102-$F102*E$103/$F$103</f>
@@ -18550,11 +18156,11 @@
         <v>-4</v>
       </c>
       <c r="G110">
-        <f>G102-$F102*G$103/$F$103</f>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="I110" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J110">
         <v>-3</v>
@@ -18570,7 +18176,7 @@
     </row>
     <row r="111" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D111" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -18579,11 +18185,11 @@
         <v>1</v>
       </c>
       <c r="G111">
-        <f>G103-$F103*G$103/$F$103</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I111" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="J111">
         <v>1</v>
@@ -18597,7 +18203,7 @@
     </row>
     <row r="112" spans="2:12" x14ac:dyDescent="0.25">
       <c r="D112" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E112" s="27">
         <f>E104-$F104*E$103/$F$103</f>
@@ -18607,27 +18213,27 @@
         <v>0</v>
       </c>
       <c r="G112">
-        <f>G104-$F104*G$103/$F$103</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="I112" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J112">
         <v>0</v>
       </c>
       <c r="K112" s="27">
-        <f>K104-$J104*K$103/$J$103</f>
+        <f t="shared" ref="K112:L114" si="5">K104-$J104*K$103/$J$103</f>
         <v>1</v>
       </c>
       <c r="L112">
-        <f>L104-$J104*L$103/$J$103</f>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
     </row>
     <row r="113" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D113" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E113">
         <f>E105-$F105*E$103/$F$103</f>
@@ -18637,27 +18243,27 @@
         <v>0</v>
       </c>
       <c r="G113">
-        <f>G105-$F105*G$103/$F$103</f>
+        <f t="shared" si="4"/>
         <v>-9</v>
       </c>
       <c r="I113" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="J113">
         <v>0</v>
       </c>
       <c r="K113">
-        <f>K105-$J105*K$103/$J$103</f>
+        <f t="shared" si="5"/>
         <v>-1</v>
       </c>
       <c r="L113">
-        <f>L105-$J105*L$103/$J$103</f>
+        <f t="shared" si="5"/>
         <v>-9</v>
       </c>
     </row>
     <row r="114" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D114" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E114">
         <f>E106-$F106*E$103/$F$103</f>
@@ -18667,39 +18273,39 @@
         <v>18</v>
       </c>
       <c r="G114">
-        <f>G106-$F106*G$103/$F$103</f>
+        <f t="shared" si="4"/>
         <v>144</v>
       </c>
       <c r="I114" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="J114">
         <v>14</v>
       </c>
       <c r="K114">
-        <f>K106-$J106*K$103/$J$103</f>
+        <f t="shared" si="5"/>
         <v>-18</v>
       </c>
       <c r="L114">
-        <f>L106-$J106*L$103/$J$103</f>
+        <f t="shared" si="5"/>
         <v>98</v>
       </c>
     </row>
     <row r="116" spans="4:12" x14ac:dyDescent="0.25">
       <c r="E116" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F116" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G116">
         <v>1</v>
       </c>
       <c r="J116" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="K116" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="L116">
         <v>1</v>
@@ -18707,21 +18313,21 @@
     </row>
     <row r="117" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D117" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E117">
         <v>-2</v>
       </c>
       <c r="F117">
-        <f>F109-$E109*F$112/$E$112</f>
+        <f t="shared" ref="F117:G119" si="6">F109-$E109*F$112/$E$112</f>
         <v>-2</v>
       </c>
       <c r="G117">
-        <f>G109-$E109*G$112/$E$112</f>
+        <f t="shared" si="6"/>
         <v>-1</v>
       </c>
       <c r="I117" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="J117">
         <v>-2</v>
@@ -18735,21 +18341,21 @@
     </row>
     <row r="118" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D118" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E118">
         <v>-3</v>
       </c>
       <c r="F118">
-        <f>F110-$E110*F$112/$E$112</f>
+        <f t="shared" si="6"/>
         <v>-4</v>
       </c>
       <c r="G118">
-        <f>G110-$E110*G$112/$E$112</f>
+        <f t="shared" si="6"/>
         <v>-1</v>
       </c>
       <c r="I118" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J118">
         <v>-3</v>
@@ -18763,21 +18369,21 @@
     </row>
     <row r="119" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D119" t="s">
+        <v>50</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="G119">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I119" t="s">
         <v>57</v>
-      </c>
-      <c r="E119">
-        <v>0</v>
-      </c>
-      <c r="F119">
-        <f>F111-$E111*F$112/$E$112</f>
-        <v>1</v>
-      </c>
-      <c r="G119">
-        <f>G111-$E111*G$112/$E$112</f>
-        <v>0</v>
-      </c>
-      <c r="I119" t="s">
-        <v>64</v>
       </c>
       <c r="J119">
         <v>1</v>
@@ -18791,7 +18397,7 @@
     </row>
     <row r="120" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D120" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E120" s="27">
         <f>E112-$F112*E$103/$F$103</f>
@@ -18805,7 +18411,7 @@
         <v>9</v>
       </c>
       <c r="I120" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -18819,7 +18425,7 @@
     </row>
     <row r="121" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D121" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E121">
         <v>1</v>
@@ -18833,7 +18439,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -18847,7 +18453,7 @@
     </row>
     <row r="122" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D122" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E122">
         <v>14</v>
@@ -18861,7 +18467,7 @@
         <v>270</v>
       </c>
       <c r="I122" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="J122">
         <v>14</v>
@@ -18880,7 +18486,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE12E056-F3F5-4869-A90A-8F58804BBB0B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AH81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -18906,7 +18512,7 @@
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B2" s="74">
         <f>V45</f>
@@ -18937,16 +18543,16 @@
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="R4" s="90" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="S4" s="89"/>
       <c r="T4" s="91">
@@ -18976,7 +18582,7 @@
         <v>5.4598029975571919E-3</v>
       </c>
       <c r="R5" s="87" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="S5" s="86"/>
       <c r="T5" s="83">
@@ -18997,7 +18603,7 @@
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B6">
         <v>0.15321672361880467</v>
@@ -19016,10 +18622,10 @@
         <v>0.53269999999999995</v>
       </c>
       <c r="R6" s="84" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="S6" s="84" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="T6" s="83">
         <v>5.13</v>
@@ -19037,25 +18643,25 @@
         <v>49.481000000000002</v>
       </c>
       <c r="AB6" s="90" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="AC6" s="87" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="AD6" s="84" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="AE6" s="87" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="AF6" s="84" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="AG6" s="87" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="AH6" s="84" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
@@ -19075,7 +18681,7 @@
         <v>1</v>
       </c>
       <c r="R7" s="87" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="S7" s="86"/>
       <c r="T7" s="83">
@@ -19117,7 +18723,7 @@
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B8">
         <f>B1*B5*B5+B2*B5*C5+B3*B5*D5</f>
@@ -19136,10 +18742,10 @@
         <v>0.37294920221510963</v>
       </c>
       <c r="R8" s="84" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="S8" s="84" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="T8" s="83">
         <v>35.729999999999997</v>
@@ -19180,7 +18786,7 @@
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.25">
       <c r="R9" s="87" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="S9" s="86"/>
       <c r="T9" s="83">
@@ -19222,10 +18828,10 @@
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.25">
       <c r="R10" s="84" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="S10" s="84" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="T10" s="83">
         <v>8.02</v>
@@ -19266,7 +18872,7 @@
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="R11" s="90" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="S11" s="89"/>
       <c r="T11" s="88">
@@ -19308,7 +18914,7 @@
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.25">
       <c r="R12" s="87" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="S12" s="86"/>
       <c r="T12" s="83">
@@ -19350,10 +18956,10 @@
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.25">
       <c r="R13" s="84" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="S13" s="84" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="T13" s="83">
         <v>20.92</v>
@@ -19394,7 +19000,7 @@
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.25">
       <c r="R14" s="87" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="S14" s="86"/>
       <c r="T14" s="83">
@@ -19436,10 +19042,10 @@
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.25">
       <c r="R15" s="84" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="S15" s="84" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="T15" s="83">
         <v>20.88</v>
@@ -19480,7 +19086,7 @@
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.25">
       <c r="R16" s="87" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="S16" s="86"/>
       <c r="T16" s="83">
@@ -19522,10 +19128,10 @@
     </row>
     <row r="17" spans="11:26" x14ac:dyDescent="0.25">
       <c r="R17" s="84" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="S17" s="84" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="T17" s="83">
         <v>21.43</v>
@@ -19546,372 +19152,372 @@
     <row r="18" spans="11:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="11:26" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="R19" s="80" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="S19" s="79" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="T19" s="79" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="U19" s="79" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="V19" s="79" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="W19" s="79" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="11:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="R20" s="78">
-        <f>(AC8-AC7+AD7)/AC7</f>
+        <f t="shared" ref="R20:R28" si="0">(AC8-AC7+AD7)/AC7</f>
         <v>-0.25648351648351647</v>
       </c>
       <c r="S20" s="78">
-        <f>(AE8-AE7+AF7)/AE7</f>
+        <f t="shared" ref="S20:S28" si="1">(AE8-AE7+AF7)/AE7</f>
         <v>0.57999999999999996</v>
       </c>
       <c r="T20" s="78">
-        <f>(AG8-AG7+AH7)/AG7</f>
+        <f t="shared" ref="T20:T28" si="2">(AG8-AG7+AH7)/AG7</f>
         <v>-0.43369047619047629</v>
       </c>
       <c r="U20" s="77">
-        <f>R20-N32</f>
+        <f t="shared" ref="U20:U28" si="3">R20-N32</f>
         <v>-0.42672432050441056</v>
       </c>
       <c r="V20" s="77">
-        <f>S20-O32</f>
+        <f t="shared" ref="V20:V28" si="4">S20-O32</f>
         <v>-6.0858429062435326E-2</v>
       </c>
       <c r="W20" s="77">
-        <f>T20-P32</f>
+        <f t="shared" ref="W20:W28" si="5">T20-P32</f>
         <v>-0.87448179481249189</v>
       </c>
       <c r="X20">
-        <f>U20*U20</f>
+        <f t="shared" ref="X20:X29" si="6">U20*U20</f>
         <v>0.1820936457099509</v>
       </c>
       <c r="Y20">
-        <f>V20*V20</f>
+        <f t="shared" ref="Y20:Y29" si="7">V20*V20</f>
         <v>3.703748387947473E-3</v>
       </c>
       <c r="Z20">
-        <f>W20*W20</f>
+        <f t="shared" ref="Z20:Z29" si="8">W20*W20</f>
         <v>0.76471840945847713</v>
       </c>
     </row>
     <row r="21" spans="11:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="R21" s="78">
-        <f>(AC9-AC8+AD8)/AC8</f>
+        <f t="shared" si="0"/>
         <v>-0.25635694866464098</v>
       </c>
       <c r="S21" s="78">
-        <f>(AE9-AE8+AF8)/AE8</f>
+        <f t="shared" si="1"/>
         <v>0.18023083752589522</v>
       </c>
       <c r="T21" s="78">
-        <f>(AG9-AG8+AH8)/AG8</f>
+        <f t="shared" si="2"/>
         <v>0.56611883691529719</v>
       </c>
       <c r="U21" s="77">
-        <f>R21-N33</f>
+        <f t="shared" si="3"/>
         <v>-0.25635694866464098</v>
       </c>
       <c r="V21" s="77">
-        <f>S21-O33</f>
+        <f t="shared" si="4"/>
         <v>0.18023083752589522</v>
       </c>
       <c r="W21" s="77">
-        <f>T21-P33</f>
+        <f t="shared" si="5"/>
         <v>0.56611883691529719</v>
       </c>
       <c r="X21">
-        <f>U21*U21</f>
+        <f t="shared" si="6"/>
         <v>6.5718885128645377E-2</v>
       </c>
       <c r="Y21">
-        <f>V21*V21</f>
+        <f t="shared" si="7"/>
         <v>3.2483154795285643E-2</v>
       </c>
       <c r="Z21">
-        <f>W21*W21</f>
+        <f t="shared" si="8"/>
         <v>0.32049053751032885</v>
       </c>
     </row>
     <row r="22" spans="11:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="R22" s="78">
-        <f>(AC10-AC9+AD9)/AC9</f>
+        <f t="shared" si="0"/>
         <v>-0.25658648339060702</v>
       </c>
       <c r="S22" s="78">
-        <f>(AE10-AE9+AF9)/AE9</f>
+        <f t="shared" si="1"/>
         <v>1.1798649478207492</v>
       </c>
       <c r="T22" s="78">
-        <f>(AG10-AG9+AH9)/AG9</f>
+        <f t="shared" si="2"/>
         <v>0.1659538066723695</v>
       </c>
       <c r="U22" s="77">
-        <f>R22-N34</f>
+        <f t="shared" si="3"/>
         <v>-0.25658648339060702</v>
       </c>
       <c r="V22" s="77">
-        <f>S22-O34</f>
+        <f t="shared" si="4"/>
         <v>1.1798649478207492</v>
       </c>
       <c r="W22" s="77">
-        <f>T22-P34</f>
+        <f t="shared" si="5"/>
         <v>0.1659538066723695</v>
       </c>
       <c r="X22">
-        <f>U22*U22</f>
+        <f t="shared" si="6"/>
         <v>6.5836623458758251E-2</v>
       </c>
       <c r="Y22">
-        <f>V22*V22</f>
+        <f t="shared" si="7"/>
         <v>1.3920812950960593</v>
       </c>
       <c r="Z22">
-        <f>W22*W22</f>
+        <f t="shared" si="8"/>
         <v>2.7540665949050191E-2</v>
       </c>
     </row>
     <row r="23" spans="11:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K23" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="L23" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="M23" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="R23" s="78">
-        <f>(AC11-AC10+AD10)/AC10</f>
+        <f t="shared" si="0"/>
         <v>0.58952234206471488</v>
       </c>
       <c r="S23" s="78">
-        <f>(AE11-AE10+AF10)/AE10</f>
+        <f t="shared" si="1"/>
         <v>0.42346323824829246</v>
       </c>
       <c r="T23" s="78">
-        <f>(AG11-AG10+AH10)/AG10</f>
+        <f t="shared" si="2"/>
         <v>0.37256637168141604</v>
       </c>
       <c r="U23" s="77">
-        <f>R23-N35</f>
+        <f t="shared" si="3"/>
         <v>0.58952234206471488</v>
       </c>
       <c r="V23" s="77">
-        <f>S23-O35</f>
+        <f t="shared" si="4"/>
         <v>0.42346323824829246</v>
       </c>
       <c r="W23" s="77">
-        <f>T23-P35</f>
+        <f t="shared" si="5"/>
         <v>0.37256637168141604</v>
       </c>
       <c r="X23">
-        <f>U23*U23</f>
+        <f t="shared" si="6"/>
         <v>0.34753659179346669</v>
       </c>
       <c r="Y23">
-        <f>V23*V23</f>
+        <f t="shared" si="7"/>
         <v>0.17932111414773011</v>
       </c>
       <c r="Z23">
-        <f>W23*W23</f>
+        <f t="shared" si="8"/>
         <v>0.13880570130785505</v>
       </c>
     </row>
     <row r="24" spans="11:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="R24" s="78">
-        <f>(AC12-AC11+AD11)/AC11</f>
+        <f t="shared" si="0"/>
         <v>0.64361309377307396</v>
       </c>
       <c r="S24" s="78">
-        <f>(AE12-AE11+AF11)/AE11</f>
+        <f t="shared" si="1"/>
         <v>0.87997302764666219</v>
       </c>
       <c r="T24" s="78">
-        <f>(AG12-AG11+AH11)/AG11</f>
+        <f t="shared" si="2"/>
         <v>0.66625217607560305</v>
       </c>
       <c r="U24" s="77">
-        <f>R24-N36</f>
+        <f t="shared" si="3"/>
         <v>0.64361309377307396</v>
       </c>
       <c r="V24" s="77">
-        <f>S24-O36</f>
+        <f t="shared" si="4"/>
         <v>0.87997302764666219</v>
       </c>
       <c r="W24" s="77">
-        <f>T24-P36</f>
+        <f t="shared" si="5"/>
         <v>0.66625217607560305</v>
       </c>
       <c r="X24">
-        <f>U24*U24</f>
+        <f t="shared" si="6"/>
         <v>0.41423781447614771</v>
       </c>
       <c r="Y24">
-        <f>V24*V24</f>
+        <f t="shared" si="7"/>
         <v>0.77435252938563326</v>
       </c>
       <c r="Z24">
-        <f>W24*W24</f>
+        <f t="shared" si="8"/>
         <v>0.44389196212547638</v>
       </c>
     </row>
     <row r="25" spans="11:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="R25" s="78">
-        <f>(AC13-AC12+AD12)/AC12</f>
+        <f t="shared" si="0"/>
         <v>-5.6258177060619252E-2</v>
       </c>
       <c r="S25" s="78">
-        <f>(AE13-AE12+AF12)/AE12</f>
+        <f t="shared" si="1"/>
         <v>1.1797591743119265</v>
       </c>
       <c r="T25" s="78">
-        <f>(AG13-AG12+AH12)/AG12</f>
+        <f t="shared" si="2"/>
         <v>-0.23392582839587447</v>
       </c>
       <c r="U25" s="77">
-        <f>R25-N37</f>
+        <f t="shared" si="3"/>
         <v>-5.6258177060619252E-2</v>
       </c>
       <c r="V25" s="77">
-        <f>S25-O37</f>
+        <f t="shared" si="4"/>
         <v>1.1797591743119265</v>
       </c>
       <c r="W25" s="77">
-        <f>T25-P37</f>
+        <f t="shared" si="5"/>
         <v>-0.23392582839587447</v>
       </c>
       <c r="X25">
-        <f>U25*U25</f>
+        <f t="shared" si="6"/>
         <v>3.1649824861839861E-3</v>
       </c>
       <c r="Y25">
-        <f>V25*V25</f>
+        <f t="shared" si="7"/>
         <v>1.3918317093731585</v>
       </c>
       <c r="Z25">
-        <f>W25*W25</f>
+        <f t="shared" si="8"/>
         <v>5.4721293190696116E-2</v>
       </c>
     </row>
     <row r="26" spans="11:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="R26" s="78">
-        <f>(AC14-AC13+AD13)/AC13</f>
+        <f t="shared" si="0"/>
         <v>0.84336221025520941</v>
       </c>
       <c r="S26" s="78">
-        <f>(AE14-AE13+AF13)/AE13</f>
+        <f t="shared" si="1"/>
         <v>0.47993504987241942</v>
       </c>
       <c r="T26" s="78">
-        <f>(AG14-AG13+AH13)/AG13</f>
+        <f t="shared" si="2"/>
         <v>0.26619588578446418</v>
       </c>
       <c r="U26" s="77">
-        <f>R26-N38</f>
+        <f t="shared" si="3"/>
         <v>0.84336221025520941</v>
       </c>
       <c r="V26" s="77">
-        <f>S26-O38</f>
+        <f t="shared" si="4"/>
         <v>0.47993504987241942</v>
       </c>
       <c r="W26" s="77">
-        <f>T26-P38</f>
+        <f t="shared" si="5"/>
         <v>0.26619588578446418</v>
       </c>
       <c r="X26">
-        <f>U26*U26</f>
+        <f t="shared" si="6"/>
         <v>0.711259817686552</v>
       </c>
       <c r="Y26">
-        <f>V26*V26</f>
+        <f t="shared" si="7"/>
         <v>0.23033765209604171</v>
       </c>
       <c r="Z26">
-        <f>W26*W26</f>
+        <f t="shared" si="8"/>
         <v>7.0860249608575496E-2</v>
       </c>
     </row>
     <row r="27" spans="11:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="R27" s="78">
-        <f>(AC15-AC14+AD14)/AC14</f>
+        <f t="shared" si="0"/>
         <v>0.54355840512923259</v>
       </c>
       <c r="S27" s="78">
-        <f>(AE15-AE14+AF14)/AE14</f>
+        <f t="shared" si="1"/>
         <v>7.9873015873015929E-2</v>
       </c>
       <c r="T27" s="78">
-        <f>(AG15-AG14+AH14)/AG14</f>
+        <f t="shared" si="2"/>
         <v>-3.3586005830903702E-2</v>
       </c>
       <c r="U27" s="77">
-        <f>R27-N39</f>
+        <f t="shared" si="3"/>
         <v>0.54355840512923259</v>
       </c>
       <c r="V27" s="77">
-        <f>S27-O39</f>
+        <f t="shared" si="4"/>
         <v>7.9873015873015929E-2</v>
       </c>
       <c r="W27" s="77">
-        <f>T27-P39</f>
+        <f t="shared" si="5"/>
         <v>-3.3586005830903702E-2</v>
       </c>
       <c r="X27">
-        <f>U27*U27</f>
+        <f t="shared" si="6"/>
         <v>0.29545573978663497</v>
       </c>
       <c r="Y27">
-        <f>V27*V27</f>
+        <f t="shared" si="7"/>
         <v>6.3796986646510543E-3</v>
       </c>
       <c r="Z27">
-        <f>W27*W27</f>
+        <f t="shared" si="8"/>
         <v>1.1280197876734975E-3</v>
       </c>
     </row>
     <row r="28" spans="11:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="R28" s="78">
-        <f>(AC16-AC15+AD15)/AC15</f>
+        <f t="shared" si="0"/>
         <v>-0.26220368943480021</v>
       </c>
       <c r="S28" s="78">
-        <f>(AE16-AE15+AF15)/AE15</f>
+        <f t="shared" si="1"/>
         <v>0.78462657026295579</v>
       </c>
       <c r="T28" s="78">
-        <f>(AG16-AG15+AH15)/AG15</f>
+        <f t="shared" si="2"/>
         <v>2.6312371008862456</v>
       </c>
       <c r="U28" s="77">
-        <f>R28-N40</f>
+        <f t="shared" si="3"/>
         <v>-0.26220368943480021</v>
       </c>
       <c r="V28" s="77">
-        <f>S28-O40</f>
+        <f t="shared" si="4"/>
         <v>0.78462657026295579</v>
       </c>
       <c r="W28" s="77">
-        <f>T28-P40</f>
+        <f t="shared" si="5"/>
         <v>2.6312371008862456</v>
       </c>
       <c r="X28">
-        <f>U28*U28</f>
+        <f t="shared" si="6"/>
         <v>6.8750774753221167E-2</v>
       </c>
       <c r="Y28">
-        <f>V28*V28</f>
+        <f t="shared" si="7"/>
         <v>0.61563885476260916</v>
       </c>
       <c r="Z28">
-        <f>W28*W28</f>
+        <f t="shared" si="8"/>
         <v>6.9234086810802546</v>
       </c>
     </row>
@@ -19923,15 +19529,15 @@
       <c r="V29" s="77"/>
       <c r="W29" s="77"/>
       <c r="X29">
-        <f>U29*U29</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Y29">
-        <f>V29*V29</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="Z29">
-        <f>W29*W29</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -20006,77 +19612,77 @@
         <v>12</v>
       </c>
       <c r="V34">
-        <f>U20*V20</f>
+        <f t="shared" ref="V34:V43" si="9">U20*V20</f>
         <v>2.5969771788633588E-2</v>
       </c>
       <c r="W34">
         <v>13</v>
       </c>
       <c r="X34">
-        <f>U20*W20</f>
+        <f t="shared" ref="X34:X43" si="10">U20*W20</f>
         <v>0.37316264968483798</v>
       </c>
       <c r="Y34">
         <v>23</v>
       </c>
       <c r="Z34">
-        <f>V20*W20</f>
+        <f t="shared" ref="Z34:Z43" si="11">V20*W20</f>
         <v>5.3219588275987162E-2</v>
       </c>
     </row>
     <row r="35" spans="4:26" x14ac:dyDescent="0.25">
       <c r="V35">
-        <f>U21*V21</f>
+        <f t="shared" si="9"/>
         <v>-4.620342756341117E-2</v>
       </c>
       <c r="X35">
-        <f>U21*W21</f>
+        <f t="shared" si="10"/>
         <v>-0.14512849761318111</v>
       </c>
       <c r="Z35">
-        <f>V21*W21</f>
+        <f t="shared" si="11"/>
         <v>0.1020320721164297</v>
       </c>
     </row>
     <row r="36" spans="4:26" x14ac:dyDescent="0.25">
       <c r="V36">
-        <f>U22*V22</f>
+        <f t="shared" si="9"/>
         <v>-0.30273739783716808</v>
       </c>
       <c r="X36">
-        <f>U22*W22</f>
+        <f t="shared" si="10"/>
         <v>-4.2581503659347944E-2</v>
       </c>
       <c r="Z36">
-        <f>V22*W22</f>
+        <f t="shared" si="11"/>
         <v>0.19580307945014996</v>
       </c>
     </row>
     <row r="37" spans="4:26" x14ac:dyDescent="0.25">
       <c r="V37">
-        <f>U23*V23</f>
+        <f t="shared" si="9"/>
         <v>0.24964103999044171</v>
       </c>
       <c r="X37">
-        <f>U23*W23</f>
+        <f t="shared" si="10"/>
         <v>0.21963620000818146</v>
       </c>
       <c r="Z37">
-        <f>V23*W23</f>
+        <f t="shared" si="11"/>
         <v>0.15776816221462936</v>
       </c>
     </row>
     <row r="38" spans="4:26" x14ac:dyDescent="0.25">
       <c r="V38">
-        <f>U24*V24</f>
+        <f t="shared" si="9"/>
         <v>0.56636216276052698</v>
       </c>
       <c r="X38">
-        <f>U24*W24</f>
+        <f t="shared" si="10"/>
         <v>0.42880862427706168</v>
       </c>
       <c r="Z38">
-        <f>V24*W24</f>
+        <f t="shared" si="11"/>
         <v>0.5862839445574255</v>
       </c>
     </row>
@@ -20094,58 +19700,58 @@
         <v>3.967121867598141</v>
       </c>
       <c r="V39">
-        <f>U25*V25</f>
+        <f t="shared" si="9"/>
         <v>-6.6371100517330334E-2</v>
       </c>
       <c r="X39">
-        <f>U25*W25</f>
+        <f t="shared" si="10"/>
         <v>1.3160240672947141E-2</v>
       </c>
       <c r="Z39">
-        <f>V25*W25</f>
+        <f t="shared" si="11"/>
         <v>-0.27597614215855026</v>
       </c>
     </row>
     <row r="40" spans="4:26" x14ac:dyDescent="0.25">
       <c r="V40">
-        <f>U26*V26</f>
+        <f t="shared" si="9"/>
         <v>0.40475908443934777</v>
       </c>
       <c r="X40">
-        <f>U26*W26</f>
+        <f t="shared" si="10"/>
         <v>0.224499550596029</v>
       </c>
       <c r="Z40">
-        <f>V26*W26</f>
+        <f t="shared" si="11"/>
         <v>0.12775673571979967</v>
       </c>
     </row>
     <row r="41" spans="4:26" x14ac:dyDescent="0.25">
       <c r="E41" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F41" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G41" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="V41">
-        <f>U27*V27</f>
+        <f t="shared" si="9"/>
         <v>4.341564912079842E-2</v>
       </c>
       <c r="X41">
-        <f>U27*W27</f>
+        <f t="shared" si="10"/>
         <v>-1.8255955764107122E-2</v>
       </c>
       <c r="Z41">
-        <f>V27*W27</f>
+        <f t="shared" si="11"/>
         <v>-2.6826155768429768E-3</v>
       </c>
     </row>
     <row r="42" spans="4:26" x14ac:dyDescent="0.25">
       <c r="D42" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E42">
         <v>-0.17</v>
@@ -20164,21 +19770,21 @@
         <v>0.34543778999999997</v>
       </c>
       <c r="V42">
-        <f>U28*V28</f>
+        <f t="shared" si="9"/>
         <v>-0.2057319815515205</v>
       </c>
       <c r="X42">
-        <f>U28*W28</f>
+        <f t="shared" si="10"/>
         <v>-0.68992007563010127</v>
       </c>
       <c r="Z42">
-        <f>V28*W28</f>
+        <f t="shared" si="11"/>
         <v>2.0645385420170177</v>
       </c>
     </row>
     <row r="43" spans="4:26" x14ac:dyDescent="0.25">
       <c r="D43" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -20193,15 +19799,15 @@
         <v>1</v>
       </c>
       <c r="V43">
-        <f>U29*V29</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="X43">
-        <f>U29*W29</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="Z43">
-        <f>V29*W29</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -20233,13 +19839,13 @@
     </row>
     <row r="45" spans="4:26" x14ac:dyDescent="0.25">
       <c r="E45" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F45" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G45" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="N45">
         <v>0.51</v>
@@ -20269,7 +19875,7 @@
     </row>
     <row r="46" spans="4:26" x14ac:dyDescent="0.25">
       <c r="D46" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H46">
         <f>H42/F42</f>
@@ -20295,7 +19901,7 @@
     </row>
     <row r="47" spans="4:26" x14ac:dyDescent="0.25">
       <c r="D47" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H47">
         <f>H43-H42*F43/F42</f>
@@ -20308,18 +19914,18 @@
     </row>
     <row r="51" spans="4:17" x14ac:dyDescent="0.25">
       <c r="E51" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F51" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G51" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D52" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E52">
         <v>-0.17</v>
@@ -20342,7 +19948,7 @@
     </row>
     <row r="53" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D53" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -20362,7 +19968,7 @@
     </row>
     <row r="54" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D54" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E54">
         <v>0.11509999999999999</v>
@@ -20379,13 +19985,13 @@
     </row>
     <row r="56" spans="4:17" x14ac:dyDescent="0.25">
       <c r="E56" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F56" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G56" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="J56">
         <v>0.22900000000000001</v>
@@ -20409,7 +20015,7 @@
     </row>
     <row r="57" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D57" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E57">
         <f>E52/$F$52</f>
@@ -20453,7 +20059,7 @@
     </row>
     <row r="58" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D58" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E58" s="27">
         <f>E53-E$52*$F53/$F$52</f>
@@ -20481,7 +20087,7 @@
     </row>
     <row r="59" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D59" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E59">
         <f>E54-E$52*$F54/$F$52</f>
@@ -20531,13 +20137,13 @@
     </row>
     <row r="61" spans="4:17" x14ac:dyDescent="0.25">
       <c r="E61" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F61" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G61" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="J61">
         <f>K52*J60</f>
@@ -20550,7 +20156,7 @@
     </row>
     <row r="62" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D62" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E62">
         <f>-E57/$E$58</f>
@@ -20575,7 +20181,7 @@
     </row>
     <row r="63" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D63" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E63" s="27">
         <f>1/E58</f>
@@ -20596,7 +20202,7 @@
     </row>
     <row r="64" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D64" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E64">
         <f>-E59/$E$58</f>
@@ -20689,7 +20295,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4BBF1E5-6BE7-487D-9070-F428A344626A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20700,75 +20306,75 @@
     <row r="2" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="101"/>
       <c r="B2" s="100" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C2" s="100" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D2" s="100" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="E2" s="100" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F2" s="100" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="G2" s="100" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="H2" s="100" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="I2" s="100" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="J2" s="100" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="K2" s="100" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="L2" s="100" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="M2" s="100" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="N2" s="100" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="O2" s="100" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="P2" s="100" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="Q2" s="100" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="R2" s="100" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="S2" s="100" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="T2" s="100" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="U2" s="100" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="V2" s="100" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="W2" s="99" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="97" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B3" s="139">
         <v>0</v>
@@ -20839,7 +20445,7 @@
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="97" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C4" s="92">
         <v>-1</v>
@@ -20852,7 +20458,7 @@
       </c>
       <c r="W4" s="96"/>
       <c r="X4" s="92">
-        <f>SUMPRODUCT(B$3:W$3,B4:W4)</f>
+        <f t="shared" ref="X4:X21" si="0">SUMPRODUCT(B$3:W$3,B4:W4)</f>
         <v>0</v>
       </c>
       <c r="Y4" s="92">
@@ -20861,7 +20467,7 @@
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="97" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D5" s="92">
         <v>-1</v>
@@ -20874,7 +20480,7 @@
       </c>
       <c r="W5" s="96"/>
       <c r="X5" s="92">
-        <f>SUMPRODUCT(B$3:W$3,B5:W5)</f>
+        <f t="shared" si="0"/>
         <v>-3</v>
       </c>
       <c r="Y5" s="92">
@@ -20892,7 +20498,7 @@
         <v>1</v>
       </c>
       <c r="X6" s="92">
-        <f>SUMPRODUCT(B$3:W$3,B6:W6)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y6" s="92">
@@ -20901,7 +20507,7 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="97" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E7" s="92">
         <v>-1</v>
@@ -20913,7 +20519,7 @@
         <v>1</v>
       </c>
       <c r="X7" s="92">
-        <f>SUMPRODUCT(B$3:W$3,B7:W7)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y7" s="92">
@@ -20922,7 +20528,7 @@
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="97" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E8" s="92">
         <v>1</v>
@@ -20935,7 +20541,7 @@
       </c>
       <c r="W8" s="96"/>
       <c r="X8" s="92">
-        <f>SUMPRODUCT(B$3:W$3,B8:W8)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y8" s="92">
@@ -20958,7 +20564,7 @@
       </c>
       <c r="W9" s="96"/>
       <c r="X9" s="92">
-        <f>SUMPRODUCT(B$3:W$3,B9:W9)</f>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="Y9" s="92">
@@ -20967,7 +20573,7 @@
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="97" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="G10" s="92">
         <v>-1</v>
@@ -20979,7 +20585,7 @@
         <v>1</v>
       </c>
       <c r="X10" s="92">
-        <f>SUMPRODUCT(B$3:W$3,B10:W10)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y10" s="92">
@@ -20994,7 +20600,7 @@
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="97" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="G11" s="92">
         <v>1</v>
@@ -21007,7 +20613,7 @@
       </c>
       <c r="W11" s="96"/>
       <c r="X11" s="92">
-        <f>SUMPRODUCT(B$3:W$3,B11:W11)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y11" s="92">
@@ -21022,7 +20628,7 @@
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="97" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B12" s="92">
         <v>1</v>
@@ -21032,7 +20638,7 @@
       </c>
       <c r="W12" s="96"/>
       <c r="X12" s="92">
-        <f>SUMPRODUCT(B$3:W$3,B12:W12)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y12" s="92">
@@ -21041,7 +20647,7 @@
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="97" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="I13" s="92">
         <v>1</v>
@@ -21054,7 +20660,7 @@
       </c>
       <c r="W13" s="96"/>
       <c r="X13" s="92">
-        <f>SUMPRODUCT(B$3:W$3,B13:W13)</f>
+        <f t="shared" si="0"/>
         <v>-3</v>
       </c>
       <c r="Y13" s="92">
@@ -21072,7 +20678,7 @@
         <v>1</v>
       </c>
       <c r="X14" s="92">
-        <f>SUMPRODUCT(B$3:W$3,B14:W14)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y14" s="92">
@@ -21081,7 +20687,7 @@
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="97" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="K15" s="92">
         <v>-1</v>
@@ -21093,7 +20699,7 @@
         <v>1</v>
       </c>
       <c r="X15" s="92">
-        <f>SUMPRODUCT(B$3:W$3,B15:W15)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y15" s="92">
@@ -21106,7 +20712,7 @@
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="97" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B16" s="92">
         <v>1</v>
@@ -21116,7 +20722,7 @@
       </c>
       <c r="W16" s="96"/>
       <c r="X16" s="92">
-        <f>SUMPRODUCT(B$3:W$3,B16:W16)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y16" s="92">
@@ -21129,7 +20735,7 @@
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="97" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D17" s="92">
         <v>1</v>
@@ -21142,7 +20748,7 @@
       </c>
       <c r="W17" s="96"/>
       <c r="X17" s="92">
-        <f>SUMPRODUCT(B$3:W$3,B17:W17)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y17" s="92">
@@ -21166,7 +20772,7 @@
       </c>
       <c r="W18" s="96"/>
       <c r="X18" s="92">
-        <f>SUMPRODUCT(B$3:W$3,B18:W18)</f>
+        <f t="shared" si="0"/>
         <v>-6</v>
       </c>
       <c r="Y18" s="92">
@@ -21186,7 +20792,7 @@
       </c>
       <c r="W19" s="96"/>
       <c r="X19" s="92">
-        <f>SUMPRODUCT(B$3:W$3,B19:W19)</f>
+        <f t="shared" si="0"/>
         <v>-6</v>
       </c>
       <c r="Y19" s="92">
@@ -21204,7 +20810,7 @@
         <v>1</v>
       </c>
       <c r="X20" s="92">
-        <f>SUMPRODUCT(B$3:W$3,B20:W20)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y20" s="92">
@@ -21238,7 +20844,7 @@
       <c r="V21" s="94"/>
       <c r="W21" s="93"/>
       <c r="X21" s="135">
-        <f>SUMPRODUCT(B$3:W$3,B21:W21)</f>
+        <f t="shared" si="0"/>
         <v>61</v>
       </c>
       <c r="Y21" s="92">
@@ -21247,7 +20853,7 @@
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="92" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B23" s="136">
         <v>0</v>
@@ -21313,12 +20919,12 @@
         <v>76</v>
       </c>
       <c r="AA23" s="92" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="92" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="N24" s="92" cm="1">
         <f t="array" ref="N24:W24">TRANSPOSE(M26:M35)</f>
@@ -21361,25 +20967,25 @@
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="G25" s="134" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H25" s="133" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="I25" s="132" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="J25" s="132" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="K25" s="132" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="L25" s="132" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="M25" s="130" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="Z25" s="92">
         <f>-X24</f>
@@ -21388,22 +20994,22 @@
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="131" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="B26" s="130" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C26" s="129" t="s">
+        <v>132</v>
+      </c>
+      <c r="F26" s="92">
+        <v>1</v>
+      </c>
+      <c r="G26" s="125" t="s">
+        <v>107</v>
+      </c>
+      <c r="H26" s="118" t="s">
         <v>139</v>
-      </c>
-      <c r="F26" s="92">
-        <v>1</v>
-      </c>
-      <c r="G26" s="125" t="s">
-        <v>114</v>
-      </c>
-      <c r="H26" s="118" t="s">
-        <v>146</v>
       </c>
       <c r="I26" s="128">
         <v>11</v>
@@ -21418,7 +21024,7 @@
         <v>55</v>
       </c>
       <c r="M26" s="127">
-        <f>(L26-K26)/(I26-J26)</f>
+        <f t="shared" ref="M26:M35" si="1">(L26-K26)/(I26-J26)</f>
         <v>5</v>
       </c>
       <c r="N26" s="92" cm="1">
@@ -21457,7 +21063,7 @@
         <v>-964.7</v>
       </c>
       <c r="AA26" s="92" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.25">
@@ -21474,10 +21080,10 @@
         <v>2</v>
       </c>
       <c r="G27" s="125" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="H27" s="118" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="I27" s="124">
         <v>33</v>
@@ -21492,7 +21098,7 @@
         <v>165</v>
       </c>
       <c r="M27" s="123">
-        <f>(L27-K27)/(I27-J27)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="N27" s="92" cm="1">
@@ -21531,7 +21137,7 @@
         <v>-888.7</v>
       </c>
       <c r="AA27" s="92" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
@@ -21539,7 +21145,7 @@
         <v>37</v>
       </c>
       <c r="B28" s="92">
-        <f>A27-A28</f>
+        <f t="shared" ref="B28:B43" si="2">A27-A28</f>
         <v>1</v>
       </c>
       <c r="C28" s="92">
@@ -21549,10 +21155,10 @@
         <v>3</v>
       </c>
       <c r="G28" s="125" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="H28" s="118" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="I28" s="124">
         <v>33</v>
@@ -21567,7 +21173,7 @@
         <v>165</v>
       </c>
       <c r="M28" s="123">
-        <f>(L28-K28)/(I28-J28)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -21576,21 +21182,21 @@
         <v>36</v>
       </c>
       <c r="B29" s="92">
-        <f>A28-A29</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="C29" s="92">
         <v>122.7</v>
       </c>
       <c r="F29" s="92">
-        <f>F28+1</f>
+        <f t="shared" ref="F29:F35" si="3">F28+1</f>
         <v>4</v>
       </c>
       <c r="G29" s="125" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="H29" s="118" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="I29" s="124">
         <v>11</v>
@@ -21605,7 +21211,7 @@
         <v>55</v>
       </c>
       <c r="M29" s="123">
-        <f>(L29-K29)/(I29-J29)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -21614,21 +21220,21 @@
         <v>35</v>
       </c>
       <c r="B30" s="92">
-        <f>A29-A30</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="C30" s="92">
         <v>120.8</v>
       </c>
       <c r="F30" s="92">
-        <f>F29+1</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="G30" s="125" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="H30" s="118" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="I30" s="124">
         <v>22</v>
@@ -21643,7 +21249,7 @@
         <v>110</v>
       </c>
       <c r="M30" s="123">
-        <f>(L30-K30)/(I30-J30)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -21652,18 +21258,18 @@
         <v>34</v>
       </c>
       <c r="B31" s="92">
-        <f>A30-A31</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F31" s="92">
-        <f>F30+1</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="G31" s="125" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H31" s="118" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I31" s="124">
         <v>22</v>
@@ -21678,7 +21284,7 @@
         <v>110</v>
       </c>
       <c r="M31" s="123">
-        <f>(L31-K31)/(I31-J31)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="U31" s="92">
@@ -21690,15 +21296,15 @@
         <v>33</v>
       </c>
       <c r="B32" s="92">
-        <f>A31-A32</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F32" s="92">
-        <f>F31+1</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="G32" s="125" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="H32" s="121"/>
       <c r="I32" s="124">
@@ -21714,7 +21320,7 @@
         <v>125</v>
       </c>
       <c r="M32" s="123">
-        <f>(L32-K32)/(I32-J32)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="P32" s="92">
@@ -21735,18 +21341,18 @@
         <v>32</v>
       </c>
       <c r="B33" s="92">
-        <f>A32-A33</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="F33" s="92">
-        <f>F32+1</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="G33" s="125" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="H33" s="118" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="I33" s="124">
         <v>33</v>
@@ -21761,24 +21367,24 @@
         <v>165</v>
       </c>
       <c r="M33" s="123">
-        <f>(L33-K33)/(I33-J33)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B34" s="92">
-        <f>A33-A34</f>
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
       <c r="F34" s="92">
-        <f>F33+1</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="G34" s="125" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="H34" s="118" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="I34" s="124">
         <v>17</v>
@@ -21793,21 +21399,21 @@
         <v>85</v>
       </c>
       <c r="M34" s="123">
-        <f>(L34-K34)/(I34-J34)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B35" s="92">
-        <f>A34-A35</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F35" s="92">
-        <f>F34+1</f>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="G35" s="122" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H35" s="121"/>
       <c r="I35" s="120">
@@ -21823,31 +21429,31 @@
         <v>55</v>
       </c>
       <c r="M35" s="117">
-        <f>(L35-K35)/(I35-J35)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B36" s="92">
-        <f>A35-A36</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B37" s="92">
-        <f>A36-A37</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="92">
-        <f>A37-A38</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="92">
-        <f>A38-A39</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D39" s="112"/>
@@ -21877,7 +21483,7 @@
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B40" s="92">
-        <f>A39-A40</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D40" s="111"/>
@@ -21907,7 +21513,7 @@
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B41" s="92">
-        <f>A40-A41</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D41" s="111"/>
@@ -21937,7 +21543,7 @@
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B42" s="92">
-        <f>A41-A42</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D42" s="111"/>
@@ -21967,7 +21573,7 @@
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B43" s="92">
-        <f>A42-A43</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="D43" s="111"/>
@@ -22310,7 +21916,7 @@
     <row r="59" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="60" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A60" s="101" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B60" s="100">
         <f>F40</f>
@@ -22323,7 +21929,7 @@
     </row>
     <row r="61" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="98" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B61" s="92">
         <v>1</v>
@@ -22334,7 +21940,7 @@
     </row>
     <row r="62" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="97" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B62" s="92">
         <f>G40</f>
@@ -22345,18 +21951,18 @@
         <v>0</v>
       </c>
       <c r="S62" s="107" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="T62" s="106" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="U62" s="105" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A63" s="98" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B63" s="92">
         <v>2</v>
@@ -22371,13 +21977,13 @@
         <v>0</v>
       </c>
       <c r="U63" s="104">
-        <f>AA40</f>
+        <f t="shared" ref="U63:U77" si="4">AA40</f>
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A64" s="97" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B64" s="92">
         <f>H40</f>
@@ -22391,17 +21997,17 @@
         <v>37</v>
       </c>
       <c r="T64" s="92">
-        <f>S$63-S64</f>
+        <f t="shared" ref="T64:T77" si="5">S$63-S64</f>
         <v>1</v>
       </c>
       <c r="U64" s="104">
-        <f>AA41</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="98" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B65" s="92">
         <v>3</v>
@@ -22413,17 +22019,17 @@
         <v>36</v>
       </c>
       <c r="T65" s="92">
-        <f>S$63-S65</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="U65" s="104">
-        <f>AA42</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="97" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B66" s="92">
         <f>I40</f>
@@ -22437,17 +22043,17 @@
         <v>35</v>
       </c>
       <c r="T66" s="92">
-        <f>S$63-S66</f>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="U66" s="104">
-        <f>AA43</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="98" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B67" s="92">
         <v>4</v>
@@ -22459,17 +22065,17 @@
         <v>34</v>
       </c>
       <c r="T67" s="92">
-        <f>S$63-S67</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="U67" s="104">
-        <f>AA44</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="97" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B68" s="92">
         <f>J40</f>
@@ -22483,17 +22089,17 @@
         <v>33</v>
       </c>
       <c r="T68" s="92">
-        <f>S$63-S68</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="U68" s="104">
-        <f>AA45</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="98" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B69" s="92">
         <v>5</v>
@@ -22505,17 +22111,17 @@
         <v>32</v>
       </c>
       <c r="T69" s="92">
-        <f>S$63-S69</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
       <c r="U69" s="104">
-        <f>AA46</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="97" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B70" s="92">
         <f>K40</f>
@@ -22529,17 +22135,17 @@
         <v>31</v>
       </c>
       <c r="T70" s="92">
-        <f>S$63-S70</f>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="U70" s="104">
-        <f>AA47</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="98" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B71" s="92">
         <v>6</v>
@@ -22551,17 +22157,17 @@
         <v>30</v>
       </c>
       <c r="T71" s="92">
-        <f>S$63-S71</f>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="U71" s="104">
-        <f>AA48</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="97" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B72" s="92">
         <f>L40</f>
@@ -22575,17 +22181,17 @@
         <v>29</v>
       </c>
       <c r="T72" s="92">
-        <f>S$63-S72</f>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
       <c r="U72" s="104">
-        <f>AA49</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="98" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B73" s="92">
         <v>7</v>
@@ -22597,17 +22203,17 @@
         <v>28</v>
       </c>
       <c r="T73" s="92">
-        <f>S$63-S73</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
       <c r="U73" s="104">
-        <f>AA50</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="97" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B74" s="92">
         <f>M40</f>
@@ -22621,17 +22227,17 @@
         <v>27</v>
       </c>
       <c r="T74" s="92">
-        <f>S$63-S74</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
       <c r="U74" s="104">
-        <f>AA51</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="98" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B75" s="92">
         <v>8</v>
@@ -22643,17 +22249,17 @@
         <v>26</v>
       </c>
       <c r="T75" s="92">
-        <f>S$63-S75</f>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="U75" s="104">
-        <f>AA52</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="97" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B76" s="92">
         <f>N40</f>
@@ -22667,17 +22273,17 @@
         <v>25</v>
       </c>
       <c r="T76" s="92">
-        <f>S$63-S76</f>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="U76" s="104">
-        <f>AA53</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="98" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B77" s="92">
         <v>9</v>
@@ -22689,17 +22295,17 @@
         <v>24</v>
       </c>
       <c r="T77" s="94">
-        <f>S$63-S77</f>
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
       <c r="U77" s="102">
-        <f>AA54</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="97" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B78" s="92">
         <f>O40</f>
@@ -22712,7 +22318,7 @@
     </row>
     <row r="79" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="95" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B79" s="94">
         <v>10</v>
@@ -22724,7 +22330,7 @@
     <row r="82" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="101" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B83" s="100">
         <f>F56</f>
@@ -22737,7 +22343,7 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="98" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B84" s="92">
         <v>1</v>
@@ -22748,7 +22354,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="97" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B85" s="92">
         <f>G56</f>
@@ -22761,7 +22367,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="98" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B86" s="92">
         <v>2</v>
@@ -22772,7 +22378,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="97" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B87" s="92">
         <f>H56</f>
@@ -22785,7 +22391,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="98" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B88" s="92">
         <v>3</v>
@@ -22796,7 +22402,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="97" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="B89" s="92">
         <f>I56</f>
@@ -22809,7 +22415,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="98" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B90" s="92">
         <v>4</v>
@@ -22820,7 +22426,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="97" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B91" s="92">
         <f>J56</f>
@@ -22833,7 +22439,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="98" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B92" s="92">
         <v>5</v>
@@ -22844,7 +22450,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="97" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B93" s="92">
         <f>K56</f>
@@ -22857,7 +22463,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="98" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B94" s="92">
         <v>6</v>
@@ -22868,7 +22474,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="97" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B95" s="92">
         <f>L56</f>
@@ -22881,7 +22487,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="98" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B96" s="92">
         <v>7</v>
@@ -22892,7 +22498,7 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="97" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B97" s="92">
         <f>M56</f>
@@ -22905,7 +22511,7 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="98" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B98" s="92">
         <v>8</v>
@@ -22916,7 +22522,7 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="97" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B99" s="92">
         <f>N56</f>
@@ -22929,7 +22535,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="98" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B100" s="92">
         <v>9</v>
@@ -22940,7 +22546,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="97" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B101" s="92">
         <f>O56</f>
@@ -22953,7 +22559,7 @@
     </row>
     <row r="102" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="95" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="B102" s="94">
         <v>10</v>
@@ -22970,7 +22576,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14030F4B-0CB9-447D-B807-67377F65B7EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -22979,35 +22585,35 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" t="s">
         <v>50</v>
       </c>
-      <c r="D2" t="s">
-        <v>57</v>
-      </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="B3">
         <f>I13</f>
@@ -23118,7 +22724,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B8">
         <v>20.2</v>
@@ -23151,7 +22757,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="B10">
         <v>10</v>
@@ -23177,25 +22783,25 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E12" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F12" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="G12" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -23221,7 +22827,7 @@
         <v>0.9</v>
       </c>
       <c r="H13" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="I13" s="27">
         <v>9</v>
@@ -23230,7 +22836,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -23256,7 +22862,7 @@
         <v>0.2</v>
       </c>
       <c r="H14" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="I14" s="27">
         <v>3</v>
@@ -23265,7 +22871,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -23291,7 +22897,7 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="I15" s="27">
         <v>6</v>
@@ -23300,7 +22906,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -23326,7 +22932,7 @@
         <v>0.1</v>
       </c>
       <c r="H16" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="I16" s="27">
         <v>2</v>
@@ -23335,7 +22941,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.25">
@@ -23348,27 +22954,27 @@
       <c r="B19" s="11"/>
       <c r="C19" s="10"/>
       <c r="D19" s="11" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="10" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="G19" s="9"/>
     </row>
     <row r="20" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="56" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="C20" s="55"/>
       <c r="D20" s="56" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E20" s="54" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="F20" s="55" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="G20" s="54"/>
     </row>
@@ -23406,7 +23012,7 @@
       <c r="B23" s="11"/>
       <c r="C23" s="10"/>
       <c r="D23" s="11" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="9"/>
@@ -23416,24 +23022,24 @@
     </row>
     <row r="24" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="56" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C24" s="55"/>
       <c r="D24" s="56" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="E24" s="55" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F24" s="54" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="G24" s="55" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="H24" s="55"/>
       <c r="I24" s="149" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.25">
@@ -23539,7 +23145,7 @@
       <c r="B29" s="11"/>
       <c r="C29" s="10"/>
       <c r="D29" s="11" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="E29" s="10"/>
       <c r="F29" s="9"/>
@@ -23549,24 +23155,24 @@
     </row>
     <row r="30" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="56" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C30" s="55"/>
       <c r="D30" s="56" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E30" s="55" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="F30" s="54" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G30" s="55" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="H30" s="55"/>
       <c r="I30" s="149" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.25">
@@ -23651,27 +23257,27 @@
       <c r="B35" s="11"/>
       <c r="C35" s="10"/>
       <c r="D35" s="11" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="E35" s="9"/>
       <c r="F35" s="10"/>
       <c r="G35" s="9" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="56" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C36" s="55"/>
       <c r="D36" s="56" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="E36" s="54" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="F36" s="55" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="G36" s="54"/>
     </row>
